--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU30"/>
+  <dimension ref="A1:AU27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4500,27 +4500,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-10-08 21:00:00</t>
+          <t>2026-10-08 21:30:00</t>
         </is>
       </c>
     </row>
@@ -4663,27 +4663,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -4813,495 +4813,6 @@
         <v>0</v>
       </c>
       <c r="AU27" t="inlineStr">
-        <is>
-          <t>2026-10-08 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Croatia Druga HNL</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Sesvete</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Jadran LP</t>
-        </is>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>0</v>
-      </c>
-      <c r="AB28">
-        <v>0</v>
-      </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>0</v>
-      </c>
-      <c r="AG28">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>0</v>
-      </c>
-      <c r="AK28">
-        <v>0</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>-1</v>
-      </c>
-      <c r="AN28">
-        <v>-1</v>
-      </c>
-      <c r="AO28">
-        <v>-1</v>
-      </c>
-      <c r="AP28">
-        <v>-1</v>
-      </c>
-      <c r="AQ28">
-        <v>0</v>
-      </c>
-      <c r="AR28">
-        <v>0</v>
-      </c>
-      <c r="AS28">
-        <v>0</v>
-      </c>
-      <c r="AT28">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>2026-10-08 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Fluminense</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N29">
-        <v>1.57</v>
-      </c>
-      <c r="O29">
-        <v>3.92</v>
-      </c>
-      <c r="P29">
-        <v>6.7</v>
-      </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <v>0</v>
-      </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
-      <c r="W29">
-        <v>0</v>
-      </c>
-      <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="Y29">
-        <v>0</v>
-      </c>
-      <c r="Z29">
-        <v>0</v>
-      </c>
-      <c r="AA29">
-        <v>1.98</v>
-      </c>
-      <c r="AB29">
-        <v>1.71</v>
-      </c>
-      <c r="AC29">
-        <v>0</v>
-      </c>
-      <c r="AD29">
-        <v>0</v>
-      </c>
-      <c r="AE29">
-        <v>0</v>
-      </c>
-      <c r="AF29">
-        <v>0</v>
-      </c>
-      <c r="AG29">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>0</v>
-      </c>
-      <c r="AK29">
-        <v>0</v>
-      </c>
-      <c r="AL29">
-        <v>0</v>
-      </c>
-      <c r="AM29">
-        <v>-1</v>
-      </c>
-      <c r="AN29">
-        <v>-1</v>
-      </c>
-      <c r="AO29">
-        <v>-1</v>
-      </c>
-      <c r="AP29">
-        <v>-1</v>
-      </c>
-      <c r="AQ29">
-        <v>0</v>
-      </c>
-      <c r="AR29">
-        <v>0</v>
-      </c>
-      <c r="AS29">
-        <v>0</v>
-      </c>
-      <c r="AT29">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>2026-10-08 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N30">
-        <v>1.65</v>
-      </c>
-      <c r="O30">
-        <v>4</v>
-      </c>
-      <c r="P30">
-        <v>5.36</v>
-      </c>
-      <c r="Q30">
-        <v>0</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
-      <c r="U30">
-        <v>0</v>
-      </c>
-      <c r="V30">
-        <v>0</v>
-      </c>
-      <c r="W30">
-        <v>0</v>
-      </c>
-      <c r="X30">
-        <v>0</v>
-      </c>
-      <c r="Y30">
-        <v>0</v>
-      </c>
-      <c r="Z30">
-        <v>0</v>
-      </c>
-      <c r="AA30">
-        <v>1.7</v>
-      </c>
-      <c r="AB30">
-        <v>2</v>
-      </c>
-      <c r="AC30">
-        <v>0</v>
-      </c>
-      <c r="AD30">
-        <v>0</v>
-      </c>
-      <c r="AE30">
-        <v>0</v>
-      </c>
-      <c r="AF30">
-        <v>0</v>
-      </c>
-      <c r="AG30">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>0</v>
-      </c>
-      <c r="AK30">
-        <v>0</v>
-      </c>
-      <c r="AL30">
-        <v>0</v>
-      </c>
-      <c r="AM30">
-        <v>-1</v>
-      </c>
-      <c r="AN30">
-        <v>-1</v>
-      </c>
-      <c r="AO30">
-        <v>-1</v>
-      </c>
-      <c r="AP30">
-        <v>-1</v>
-      </c>
-      <c r="AQ30">
-        <v>0</v>
-      </c>
-      <c r="AR30">
-        <v>0</v>
-      </c>
-      <c r="AS30">
-        <v>0</v>
-      </c>
-      <c r="AT30">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
         <is>
           <t>2026-10-08 21:30:00</t>
         </is>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU27"/>
+  <dimension ref="A1:AU28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-10-08 12:30:00</t>
+          <t>2026-10-08 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-10-08 14:00:00</t>
+          <t>2026-10-08 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G11">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G12">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-08 14:30:00</t>
+          <t>2026-10-08 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-10-08 16:00:00</t>
+          <t>2026-10-08 14:30:00</t>
         </is>
       </c>
     </row>
@@ -2712,22 +2712,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -2870,27 +2870,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G16">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-10-08 17:30:00</t>
+          <t>2026-10-08 16:00:00</t>
         </is>
       </c>
     </row>
@@ -3033,27 +3033,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G17">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-10-08 19:30:00</t>
+          <t>2026-10-08 17:30:00</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G19">
@@ -3522,12 +3522,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-10-08 20:00:00</t>
+          <t>2026-10-08 19:30:00</t>
         </is>
       </c>
     </row>
@@ -3685,27 +3685,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-10-08 21:00:00</t>
+          <t>2026-10-08 20:00:00</t>
         </is>
       </c>
     </row>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G25">
@@ -4500,27 +4500,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-10-08 21:30:00</t>
+          <t>2026-10-08 21:00:00</t>
         </is>
       </c>
     </row>
@@ -4678,141 +4678,304 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27">
+        <v>1.57</v>
+      </c>
+      <c r="O27">
+        <v>3.92</v>
+      </c>
+      <c r="P27">
+        <v>6.7</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>1.98</v>
+      </c>
+      <c r="AB27">
+        <v>1.71</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-1</v>
+      </c>
+      <c r="AN27">
+        <v>-1</v>
+      </c>
+      <c r="AO27">
+        <v>-1</v>
+      </c>
+      <c r="AP27">
+        <v>-1</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2026-10-08 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>Palmeiras</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Bahia</t>
         </is>
       </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N27">
+      <c r="N28">
         <v>1.65</v>
       </c>
-      <c r="O27">
+      <c r="O28">
         <v>4</v>
       </c>
-      <c r="P27">
+      <c r="P28">
         <v>5.36</v>
       </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
         <v>1.7</v>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <v>2</v>
       </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <v>0</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>0</v>
-      </c>
-      <c r="AG27">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>0</v>
-      </c>
-      <c r="AK27">
-        <v>0</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>-1</v>
-      </c>
-      <c r="AN27">
-        <v>-1</v>
-      </c>
-      <c r="AO27">
-        <v>-1</v>
-      </c>
-      <c r="AP27">
-        <v>-1</v>
-      </c>
-      <c r="AQ27">
-        <v>0</v>
-      </c>
-      <c r="AR27">
-        <v>0</v>
-      </c>
-      <c r="AS27">
-        <v>0</v>
-      </c>
-      <c r="AT27">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>-1</v>
+      </c>
+      <c r="AN28">
+        <v>-1</v>
+      </c>
+      <c r="AO28">
+        <v>-1</v>
+      </c>
+      <c r="AP28">
+        <v>-1</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
         <is>
           <t>2026-10-08 21:30:00</t>
         </is>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G26">

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU28"/>
+  <dimension ref="A1:AU26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G24">
@@ -4337,27 +4337,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-10-08 21:00:00</t>
+          <t>2026-10-08 21:30:00</t>
         </is>
       </c>
     </row>
@@ -4500,27 +4500,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -4650,332 +4650,6 @@
         <v>0</v>
       </c>
       <c r="AU26" t="inlineStr">
-        <is>
-          <t>2026-10-08 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Fluminense</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N27">
-        <v>1.57</v>
-      </c>
-      <c r="O27">
-        <v>3.92</v>
-      </c>
-      <c r="P27">
-        <v>6.7</v>
-      </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
-        <v>1.98</v>
-      </c>
-      <c r="AB27">
-        <v>1.71</v>
-      </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <v>0</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>0</v>
-      </c>
-      <c r="AG27">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>0</v>
-      </c>
-      <c r="AK27">
-        <v>0</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>-1</v>
-      </c>
-      <c r="AN27">
-        <v>-1</v>
-      </c>
-      <c r="AO27">
-        <v>-1</v>
-      </c>
-      <c r="AP27">
-        <v>-1</v>
-      </c>
-      <c r="AQ27">
-        <v>0</v>
-      </c>
-      <c r="AR27">
-        <v>0</v>
-      </c>
-      <c r="AS27">
-        <v>0</v>
-      </c>
-      <c r="AT27">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>2026-10-08 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N28">
-        <v>1.65</v>
-      </c>
-      <c r="O28">
-        <v>4</v>
-      </c>
-      <c r="P28">
-        <v>5.36</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>1.7</v>
-      </c>
-      <c r="AB28">
-        <v>2</v>
-      </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>0</v>
-      </c>
-      <c r="AG28">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>0</v>
-      </c>
-      <c r="AK28">
-        <v>0</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>-1</v>
-      </c>
-      <c r="AN28">
-        <v>-1</v>
-      </c>
-      <c r="AO28">
-        <v>-1</v>
-      </c>
-      <c r="AP28">
-        <v>-1</v>
-      </c>
-      <c r="AQ28">
-        <v>0</v>
-      </c>
-      <c r="AR28">
-        <v>0</v>
-      </c>
-      <c r="AS28">
-        <v>0</v>
-      </c>
-      <c r="AT28">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
         <is>
           <t>2026-10-08 21:30:00</t>
         </is>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU26"/>
+  <dimension ref="A1:AU24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G22">
@@ -4011,27 +4011,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4097,10 +4097,10 @@
         <v>0</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC23">
         <v>0</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-10-08 21:00:00</t>
+          <t>2026-10-08 21:30:00</t>
         </is>
       </c>
     </row>
@@ -4174,27 +4174,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4324,332 +4324,6 @@
         <v>0</v>
       </c>
       <c r="AU24" t="inlineStr">
-        <is>
-          <t>2026-10-08 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Fluminense</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N25">
-        <v>1.57</v>
-      </c>
-      <c r="O25">
-        <v>3.92</v>
-      </c>
-      <c r="P25">
-        <v>6.7</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <v>0</v>
-      </c>
-      <c r="X25">
-        <v>0</v>
-      </c>
-      <c r="Y25">
-        <v>0</v>
-      </c>
-      <c r="Z25">
-        <v>0</v>
-      </c>
-      <c r="AA25">
-        <v>1.98</v>
-      </c>
-      <c r="AB25">
-        <v>1.71</v>
-      </c>
-      <c r="AC25">
-        <v>0</v>
-      </c>
-      <c r="AD25">
-        <v>0</v>
-      </c>
-      <c r="AE25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>0</v>
-      </c>
-      <c r="AG25">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>0</v>
-      </c>
-      <c r="AK25">
-        <v>0</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>-1</v>
-      </c>
-      <c r="AN25">
-        <v>-1</v>
-      </c>
-      <c r="AO25">
-        <v>-1</v>
-      </c>
-      <c r="AP25">
-        <v>-1</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>2026-10-08 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Palmeiras</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N26">
-        <v>1.65</v>
-      </c>
-      <c r="O26">
-        <v>4</v>
-      </c>
-      <c r="P26">
-        <v>5.36</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>0</v>
-      </c>
-      <c r="Y26">
-        <v>0</v>
-      </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-      <c r="AA26">
-        <v>1.7</v>
-      </c>
-      <c r="AB26">
-        <v>2</v>
-      </c>
-      <c r="AC26">
-        <v>0</v>
-      </c>
-      <c r="AD26">
-        <v>0</v>
-      </c>
-      <c r="AE26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>0</v>
-      </c>
-      <c r="AG26">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>0</v>
-      </c>
-      <c r="AK26">
-        <v>0</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
-        <v>-1</v>
-      </c>
-      <c r="AN26">
-        <v>-1</v>
-      </c>
-      <c r="AO26">
-        <v>-1</v>
-      </c>
-      <c r="AP26">
-        <v>-1</v>
-      </c>
-      <c r="AQ26">
-        <v>0</v>
-      </c>
-      <c r="AR26">
-        <v>0</v>
-      </c>
-      <c r="AS26">
-        <v>0</v>
-      </c>
-      <c r="AT26">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
         <is>
           <t>2026-10-08 21:30:00</t>
         </is>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -2926,34 +2926,34 @@
         <v>7.5</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="AA16">
         <v>1.72</v>
@@ -2962,19 +2962,19 @@
         <v>2.07</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3252,34 +3252,34 @@
         <v>1.95</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA18">
         <v>1.8</v>
@@ -3288,19 +3288,19 @@
         <v>1.88</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="O19">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="P19">
-        <v>3.14</v>
+        <v>2.76</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA19">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="AB19">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="O20">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="P20">
-        <v>2.76</v>
+        <v>3.14</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA20">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AB20">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,34 +3741,34 @@
         <v>3.95</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA21">
         <v>2.05</v>
@@ -3777,19 +3777,19 @@
         <v>1.66</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4067,34 +4067,34 @@
         <v>6.7</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA23">
         <v>1.98</v>
@@ -4103,19 +4103,19 @@
         <v>1.71</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,34 +4230,34 @@
         <v>5.36</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA24">
         <v>1.7</v>
@@ -4266,19 +4266,19 @@
         <v>2</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL24">
         <v>0</v>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="O23">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="P23">
-        <v>6.7</v>
+        <v>5.36</v>
       </c>
       <c r="Q23">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="R23">
-        <v>2.13</v>
+        <v>2.29</v>
       </c>
       <c r="S23">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="V23">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z23">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA23">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="AB23">
+        <v>2</v>
+      </c>
+      <c r="AC23">
+        <v>2.49</v>
+      </c>
+      <c r="AD23">
+        <v>1.42</v>
+      </c>
+      <c r="AE23">
+        <v>1.14</v>
+      </c>
+      <c r="AF23">
         <v>1.71</v>
       </c>
-      <c r="AC23">
-        <v>3.2</v>
-      </c>
-      <c r="AD23">
-        <v>1.3</v>
-      </c>
-      <c r="AE23">
-        <v>1.08</v>
-      </c>
-      <c r="AF23">
-        <v>1.95</v>
-      </c>
       <c r="AG23">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK23">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="O24">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="P24">
-        <v>5.36</v>
+        <v>6.7</v>
       </c>
       <c r="Q24">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="R24">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T24">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U24">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="V24">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA24">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AB24">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AC24">
-        <v>2.49</v>
+        <v>3.2</v>
       </c>
       <c r="AD24">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE24">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF24">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AG24">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK24">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="AL24">
         <v>0</v>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU24"/>
+  <dimension ref="A1:AU23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.6</v>
+        <v>1.69</v>
       </c>
       <c r="O14">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P14">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="Q14">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R14">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S14">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="T14">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="U14">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="V14">
         <v>1.43</v>
       </c>
       <c r="W14">
+        <v>1.09</v>
+      </c>
+      <c r="X14">
         <v>1.02</v>
-      </c>
-      <c r="X14">
-        <v>1.05</v>
       </c>
       <c r="Y14">
         <v>1.25</v>
       </c>
       <c r="Z14">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="AA14">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB14">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AC14">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AD14">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF14">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AG14">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK14">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3406,31 +3406,31 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="O19">
-        <v>3.68</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>2.76</v>
+        <v>2.4</v>
       </c>
       <c r="Q19">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="R19">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="S19">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
         <v>3.03</v>
       </c>
       <c r="U19">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="V19">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
         <v>1.06</v>
@@ -3445,19 +3445,19 @@
         <v>3.34</v>
       </c>
       <c r="AA19">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AB19">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AC19">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="AD19">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE19">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF19">
         <v>1.68</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
         <v>1.4</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="O20">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P20">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="Q20">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="R20">
         <v>1.95</v>
@@ -3608,25 +3608,25 @@
         <v>2.52</v>
       </c>
       <c r="AA20">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB20">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC20">
         <v>4.43</v>
       </c>
       <c r="AD20">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE20">
         <v>1.03</v>
       </c>
       <c r="AF20">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AG20">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.33</v>
       </c>
       <c r="AK20">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3848,27 +3848,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-10-08 21:00:00</t>
+          <t>2026-10-08 21:30:00</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="O23">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="P23">
-        <v>5.36</v>
+        <v>6.7</v>
       </c>
       <c r="Q23">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="R23">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T23">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U23">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="V23">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z23">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA23">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AB23">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AC23">
-        <v>2.49</v>
+        <v>3.2</v>
       </c>
       <c r="AD23">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE23">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF23">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AG23">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4161,169 +4161,6 @@
         <v>0</v>
       </c>
       <c r="AU23" t="inlineStr">
-        <is>
-          <t>2026-10-08 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Fluminense</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Coritiba</t>
-        </is>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N24">
-        <v>1.57</v>
-      </c>
-      <c r="O24">
-        <v>3.92</v>
-      </c>
-      <c r="P24">
-        <v>6.7</v>
-      </c>
-      <c r="Q24">
-        <v>1.95</v>
-      </c>
-      <c r="R24">
-        <v>2.13</v>
-      </c>
-      <c r="S24">
-        <v>1.35</v>
-      </c>
-      <c r="T24">
-        <v>3</v>
-      </c>
-      <c r="U24">
-        <v>2.56</v>
-      </c>
-      <c r="V24">
-        <v>1.43</v>
-      </c>
-      <c r="W24">
-        <v>1.06</v>
-      </c>
-      <c r="X24">
-        <v>1.02</v>
-      </c>
-      <c r="Y24">
-        <v>1.25</v>
-      </c>
-      <c r="Z24">
-        <v>3.6</v>
-      </c>
-      <c r="AA24">
-        <v>1.98</v>
-      </c>
-      <c r="AB24">
-        <v>1.71</v>
-      </c>
-      <c r="AC24">
-        <v>3.2</v>
-      </c>
-      <c r="AD24">
-        <v>1.3</v>
-      </c>
-      <c r="AE24">
-        <v>1.08</v>
-      </c>
-      <c r="AF24">
-        <v>1.95</v>
-      </c>
-      <c r="AG24">
-        <v>1.75</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.22</v>
-      </c>
-      <c r="AK24">
-        <v>2.45</v>
-      </c>
-      <c r="AL24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>-1</v>
-      </c>
-      <c r="AN24">
-        <v>-1</v>
-      </c>
-      <c r="AO24">
-        <v>-1</v>
-      </c>
-      <c r="AP24">
-        <v>-1</v>
-      </c>
-      <c r="AQ24">
-        <v>0</v>
-      </c>
-      <c r="AR24">
-        <v>0</v>
-      </c>
-      <c r="AS24">
-        <v>0</v>
-      </c>
-      <c r="AT24">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
         <is>
           <t>2026-10-08 21:30:00</t>
         </is>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G4">

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="O16">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="P16">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Q16">
         <v>1.88</v>
       </c>
       <c r="R16">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="S16">
         <v>1.32</v>
@@ -2938,7 +2938,7 @@
         <v>3.18</v>
       </c>
       <c r="U16">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="V16">
         <v>1.5</v>
@@ -2956,10 +2956,10 @@
         <v>4.09</v>
       </c>
       <c r="AA16">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB16">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AC16">
         <v>2.66</v>
@@ -3243,22 +3243,22 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O18">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="P18">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q18">
         <v>4.2</v>
       </c>
       <c r="R18">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="S18">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T18">
         <v>2.87</v>
@@ -3273,7 +3273,7 @@
         <v>1.1</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
         <v>1.21</v>
@@ -3282,16 +3282,16 @@
         <v>3.9</v>
       </c>
       <c r="AA18">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB18">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AC18">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="AD18">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE18">
         <v>1.11</v>
@@ -3300,7 +3300,7 @@
         <v>1.67</v>
       </c>
       <c r="AG18">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK18">
         <v>1.24</v>
@@ -3732,25 +3732,25 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O21">
-        <v>3.43</v>
+        <v>3.35</v>
       </c>
       <c r="P21">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="Q21">
         <v>2.63</v>
       </c>
       <c r="R21">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S21">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T21">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="U21">
         <v>2.77</v>
@@ -3759,10 +3759,10 @@
         <v>1.4</v>
       </c>
       <c r="W21">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
         <v>1.3</v>
@@ -3774,13 +3774,13 @@
         <v>2.05</v>
       </c>
       <c r="AB21">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AC21">
         <v>3.6</v>
       </c>
       <c r="AD21">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE21">
         <v>1.06</v>
@@ -3895,28 +3895,28 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="O22">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P22">
-        <v>5.36</v>
+        <v>5.6</v>
       </c>
       <c r="Q22">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="R22">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T22">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U22">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="V22">
         <v>1.5</v>
@@ -3934,10 +3934,10 @@
         <v>4.4</v>
       </c>
       <c r="AA22">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB22">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC22">
         <v>2.49</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AK22">
         <v>2.32</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="O23">
-        <v>3.92</v>
+        <v>4.33</v>
       </c>
       <c r="P23">
-        <v>6.7</v>
+        <v>6.65</v>
       </c>
       <c r="Q23">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="R23">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S23">
         <v>1.35</v>
@@ -4085,25 +4085,25 @@
         <v>1.43</v>
       </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z23">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AA23">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB23">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="AC23">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AD23">
         <v>1.3</v>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -2600,16 +2600,16 @@
         <v>2.48</v>
       </c>
       <c r="Q14">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="R14">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="S14">
         <v>1.33</v>
       </c>
       <c r="T14">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="U14">
         <v>2.45</v>
@@ -2621,19 +2621,19 @@
         <v>1.09</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y14">
         <v>1.25</v>
       </c>
       <c r="Z14">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="AA14">
         <v>2.2</v>
       </c>
       <c r="AB14">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AC14">
         <v>2.78</v>
@@ -2642,10 +2642,10 @@
         <v>1.34</v>
       </c>
       <c r="AE14">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF14">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG14">
         <v>2.15</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
         <v>1.5</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="O19">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P19">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q19">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="R19">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="S19">
         <v>1.3</v>
       </c>
       <c r="T19">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="U19">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
         <v>1</v>
       </c>
       <c r="Y19">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z19">
         <v>3.34</v>
       </c>
       <c r="AA19">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB19">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC19">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="AD19">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AE19">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AG19">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AK19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O20">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P20">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="Q20">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="R20">
         <v>1.95</v>
@@ -3587,40 +3587,40 @@
         <v>1.44</v>
       </c>
       <c r="T20">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U20">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V20">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X20">
         <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="Z20">
         <v>2.52</v>
       </c>
       <c r="AA20">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AB20">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AC20">
-        <v>4.43</v>
+        <v>4.3</v>
       </c>
       <c r="AD20">
         <v>1.15</v>
       </c>
       <c r="AE20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF20">
         <v>1.98</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK20">
         <v>1.53</v>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU23"/>
+  <dimension ref="A1:AU27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,12 +588,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G2">
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-10-08 09:15:00</t>
+          <t>2026-10-08 09:00:00</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G3">
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-10-08 09:30:00</t>
+          <t>2026-10-08 09:00:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-10-08 09:30:00</t>
+          <t>2026-10-08 09:15:00</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-10-08 10:15:00</t>
+          <t>2026-10-08 09:30:00</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-10-08 10:30:00</t>
+          <t>2026-10-08 09:30:00</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-10-08 11:45:00</t>
+          <t>2026-10-08 10:15:00</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-10-08 11:45:00</t>
+          <t>2026-10-08 10:30:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-10-08 12:00:00</t>
+          <t>2026-10-08 11:45:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-10-08 12:30:00</t>
+          <t>2026-10-08 11:45:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-10-08 14:00:00</t>
+          <t>2026-10-08 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-10-08 14:00:00</t>
+          <t>2026-10-08 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-08 14:00:00</t>
+          <t>2026-10-08 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-10-08 14:30:00</t>
+          <t>2026-10-08 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-10-08 16:00:00</t>
+          <t>2026-10-08 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2870,27 +2870,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-10-08 16:00:00</t>
+          <t>2026-10-08 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G17">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-10-08 17:30:00</t>
+          <t>2026-10-08 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3196,27 +3196,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.85</v>
+        <v>1.69</v>
       </c>
       <c r="O18">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P18">
-        <v>1.85</v>
+        <v>2.48</v>
       </c>
       <c r="Q18">
-        <v>4.2</v>
+        <v>2.95</v>
       </c>
       <c r="R18">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="S18">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T18">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="U18">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V18">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="W18">
+        <v>1.09</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>1.25</v>
+      </c>
+      <c r="Z18">
+        <v>3.58</v>
+      </c>
+      <c r="AA18">
+        <v>2.2</v>
+      </c>
+      <c r="AB18">
+        <v>1.97</v>
+      </c>
+      <c r="AC18">
+        <v>2.78</v>
+      </c>
+      <c r="AD18">
+        <v>1.34</v>
+      </c>
+      <c r="AE18">
         <v>1.1</v>
       </c>
-      <c r="X18">
-        <v>1.01</v>
-      </c>
-      <c r="Y18">
-        <v>1.21</v>
-      </c>
-      <c r="Z18">
-        <v>3.9</v>
-      </c>
-      <c r="AA18">
-        <v>1.75</v>
-      </c>
-      <c r="AB18">
-        <v>1.99</v>
-      </c>
-      <c r="AC18">
-        <v>2.74</v>
-      </c>
-      <c r="AD18">
-        <v>1.35</v>
-      </c>
-      <c r="AE18">
-        <v>1.11</v>
-      </c>
       <c r="AF18">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG18">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-10-08 19:30:00</t>
+          <t>2026-10-08 14:30:00</t>
         </is>
       </c>
     </row>
@@ -3359,27 +3359,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z19">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AK19">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-10-08 19:30:00</t>
+          <t>2026-10-08 16:00:00</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="O20">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="P20">
-        <v>2.73</v>
+        <v>6.5</v>
       </c>
       <c r="Q20">
-        <v>3.01</v>
+        <v>1.83</v>
       </c>
       <c r="R20">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="S20">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="T20">
-        <v>2.39</v>
+        <v>3.22</v>
       </c>
       <c r="U20">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="V20">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="W20">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="Z20">
-        <v>2.52</v>
+        <v>3.95</v>
       </c>
       <c r="AA20">
-        <v>2.36</v>
+        <v>1.72</v>
       </c>
       <c r="AB20">
-        <v>1.54</v>
+        <v>2.12</v>
       </c>
       <c r="AC20">
-        <v>4.3</v>
+        <v>2.82</v>
       </c>
       <c r="AD20">
+        <v>1.42</v>
+      </c>
+      <c r="AE20">
         <v>1.15</v>
       </c>
-      <c r="AE20">
-        <v>1.01</v>
-      </c>
       <c r="AF20">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AG20">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AK20">
-        <v>1.53</v>
+        <v>2.88</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-10-08 19:30:00</t>
+          <t>2026-10-08 16:00:00</t>
         </is>
       </c>
     </row>
@@ -3685,27 +3685,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G21">
@@ -3728,68 +3728,68 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N21">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-10-08 20:00:00</t>
+          <t>2026-10-08 17:30:00</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.57</v>
+        <v>4.1</v>
       </c>
       <c r="O22">
+        <v>3.7</v>
+      </c>
+      <c r="P22">
+        <v>1.83</v>
+      </c>
+      <c r="Q22">
         <v>4.2</v>
       </c>
-      <c r="P22">
-        <v>5.6</v>
-      </c>
-      <c r="Q22">
-        <v>2.03</v>
-      </c>
       <c r="R22">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="S22">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T22">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="U22">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="V22">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W22">
         <v>1.1</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z22">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AA22">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AB22">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC22">
-        <v>2.49</v>
+        <v>2.9</v>
       </c>
       <c r="AD22">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AE22">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF22">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG22">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.2</v>
       </c>
       <c r="AK22">
-        <v>2.32</v>
+        <v>1.24</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-10-08 21:30:00</t>
+          <t>2026-10-08 19:30:00</t>
         </is>
       </c>
     </row>
@@ -4011,156 +4011,808 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N23">
+        <v>2.3</v>
+      </c>
+      <c r="O23">
+        <v>3</v>
+      </c>
+      <c r="P23">
+        <v>2.73</v>
+      </c>
+      <c r="Q23">
+        <v>3.01</v>
+      </c>
+      <c r="R23">
+        <v>1.95</v>
+      </c>
+      <c r="S23">
+        <v>1.44</v>
+      </c>
+      <c r="T23">
+        <v>2.39</v>
+      </c>
+      <c r="U23">
+        <v>3.4</v>
+      </c>
+      <c r="V23">
+        <v>1.27</v>
+      </c>
+      <c r="W23">
+        <v>1.01</v>
+      </c>
+      <c r="X23">
+        <v>1.05</v>
+      </c>
+      <c r="Y23">
+        <v>1.41</v>
+      </c>
+      <c r="Z23">
+        <v>2.52</v>
+      </c>
+      <c r="AA23">
+        <v>2.36</v>
+      </c>
+      <c r="AB23">
+        <v>1.54</v>
+      </c>
+      <c r="AC23">
+        <v>4.3</v>
+      </c>
+      <c r="AD23">
+        <v>1.15</v>
+      </c>
+      <c r="AE23">
+        <v>1.01</v>
+      </c>
+      <c r="AF23">
+        <v>1.98</v>
+      </c>
+      <c r="AG23">
+        <v>1.72</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>1.36</v>
+      </c>
+      <c r="AK23">
+        <v>1.53</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>-1</v>
+      </c>
+      <c r="AN23">
+        <v>-1</v>
+      </c>
+      <c r="AO23">
+        <v>-1</v>
+      </c>
+      <c r="AP23">
+        <v>-1</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N24">
+        <v>3.15</v>
+      </c>
+      <c r="O24">
+        <v>3.45</v>
+      </c>
+      <c r="P24">
+        <v>2.2</v>
+      </c>
+      <c r="Q24">
+        <v>3.5</v>
+      </c>
+      <c r="R24">
+        <v>2.15</v>
+      </c>
+      <c r="S24">
+        <v>1.3</v>
+      </c>
+      <c r="T24">
+        <v>3.1</v>
+      </c>
+      <c r="U24">
+        <v>2.5</v>
+      </c>
+      <c r="V24">
+        <v>1.44</v>
+      </c>
+      <c r="W24">
+        <v>1.07</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>1.24</v>
+      </c>
+      <c r="Z24">
+        <v>3.34</v>
+      </c>
+      <c r="AA24">
+        <v>1.85</v>
+      </c>
+      <c r="AB24">
+        <v>1.85</v>
+      </c>
+      <c r="AC24">
+        <v>3.08</v>
+      </c>
+      <c r="AD24">
+        <v>1.28</v>
+      </c>
+      <c r="AE24">
+        <v>1.07</v>
+      </c>
+      <c r="AF24">
+        <v>1.69</v>
+      </c>
+      <c r="AG24">
+        <v>2.05</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>1.57</v>
+      </c>
+      <c r="AK24">
+        <v>1.36</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>-1</v>
+      </c>
+      <c r="AN24">
+        <v>-1</v>
+      </c>
+      <c r="AO24">
+        <v>-1</v>
+      </c>
+      <c r="AP24">
+        <v>-1</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N25">
+        <v>2.05</v>
+      </c>
+      <c r="O25">
+        <v>3.35</v>
+      </c>
+      <c r="P25">
+        <v>3.6</v>
+      </c>
+      <c r="Q25">
+        <v>2.65</v>
+      </c>
+      <c r="R25">
+        <v>2.22</v>
+      </c>
+      <c r="S25">
+        <v>1.43</v>
+      </c>
+      <c r="T25">
+        <v>2.57</v>
+      </c>
+      <c r="U25">
+        <v>2.88</v>
+      </c>
+      <c r="V25">
+        <v>1.4</v>
+      </c>
+      <c r="W25">
+        <v>1.04</v>
+      </c>
+      <c r="X25">
+        <v>1.04</v>
+      </c>
+      <c r="Y25">
+        <v>1.32</v>
+      </c>
+      <c r="Z25">
+        <v>2.97</v>
+      </c>
+      <c r="AA25">
+        <v>2.04</v>
+      </c>
+      <c r="AB25">
+        <v>1.83</v>
+      </c>
+      <c r="AC25">
+        <v>3.6</v>
+      </c>
+      <c r="AD25">
+        <v>1.26</v>
+      </c>
+      <c r="AE25">
+        <v>1.06</v>
+      </c>
+      <c r="AF25">
+        <v>1.8</v>
+      </c>
+      <c r="AG25">
+        <v>1.92</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>1.24</v>
+      </c>
+      <c r="AK25">
+        <v>1.72</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-1</v>
+      </c>
+      <c r="AN25">
+        <v>-1</v>
+      </c>
+      <c r="AO25">
+        <v>-1</v>
+      </c>
+      <c r="AP25">
+        <v>-1</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2026-10-08 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N26">
+        <v>1.57</v>
+      </c>
+      <c r="O26">
+        <v>4.15</v>
+      </c>
+      <c r="P26">
+        <v>5.6</v>
+      </c>
+      <c r="Q26">
+        <v>2.03</v>
+      </c>
+      <c r="R26">
+        <v>2.54</v>
+      </c>
+      <c r="S26">
+        <v>1.29</v>
+      </c>
+      <c r="T26">
+        <v>3.22</v>
+      </c>
+      <c r="U26">
+        <v>2.29</v>
+      </c>
+      <c r="V26">
+        <v>1.5</v>
+      </c>
+      <c r="W26">
+        <v>1.11</v>
+      </c>
+      <c r="X26">
+        <v>1.03</v>
+      </c>
+      <c r="Y26">
+        <v>1.17</v>
+      </c>
+      <c r="Z26">
+        <v>4.4</v>
+      </c>
+      <c r="AA26">
+        <v>1.67</v>
+      </c>
+      <c r="AB26">
+        <v>2.15</v>
+      </c>
+      <c r="AC26">
+        <v>2.49</v>
+      </c>
+      <c r="AD26">
+        <v>1.49</v>
+      </c>
+      <c r="AE26">
+        <v>1.14</v>
+      </c>
+      <c r="AF26">
+        <v>1.73</v>
+      </c>
+      <c r="AG26">
+        <v>2</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>1.2</v>
+      </c>
+      <c r="AK26">
+        <v>2.32</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-1</v>
+      </c>
+      <c r="AN26">
+        <v>-1</v>
+      </c>
+      <c r="AO26">
+        <v>-1</v>
+      </c>
+      <c r="AP26">
+        <v>-1</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>2026-10-08 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>Fluminense</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
       </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N23">
-        <v>1.51</v>
-      </c>
-      <c r="O23">
-        <v>4.33</v>
-      </c>
-      <c r="P23">
-        <v>6.65</v>
-      </c>
-      <c r="Q23">
-        <v>1.98</v>
-      </c>
-      <c r="R23">
+      <c r="N27">
+        <v>1.48</v>
+      </c>
+      <c r="O27">
+        <v>4.4</v>
+      </c>
+      <c r="P27">
+        <v>6.5</v>
+      </c>
+      <c r="Q27">
+        <v>2.01</v>
+      </c>
+      <c r="R27">
         <v>2.25</v>
       </c>
-      <c r="S23">
+      <c r="S27">
+        <v>1.33</v>
+      </c>
+      <c r="T27">
+        <v>2.97</v>
+      </c>
+      <c r="U27">
+        <v>2.55</v>
+      </c>
+      <c r="V27">
+        <v>1.42</v>
+      </c>
+      <c r="W27">
+        <v>1.08</v>
+      </c>
+      <c r="X27">
+        <v>1</v>
+      </c>
+      <c r="Y27">
+        <v>1.24</v>
+      </c>
+      <c r="Z27">
+        <v>3.34</v>
+      </c>
+      <c r="AA27">
+        <v>1.9</v>
+      </c>
+      <c r="AB27">
+        <v>1.94</v>
+      </c>
+      <c r="AC27">
+        <v>2.97</v>
+      </c>
+      <c r="AD27">
         <v>1.35</v>
       </c>
-      <c r="T23">
-        <v>3</v>
-      </c>
-      <c r="U23">
-        <v>2.56</v>
-      </c>
-      <c r="V23">
-        <v>1.43</v>
-      </c>
-      <c r="W23">
-        <v>1.08</v>
-      </c>
-      <c r="X23">
-        <v>1</v>
-      </c>
-      <c r="Y23">
-        <v>1.24</v>
-      </c>
-      <c r="Z23">
-        <v>3.34</v>
-      </c>
-      <c r="AA23">
-        <v>1.85</v>
-      </c>
-      <c r="AB23">
-        <v>1.94</v>
-      </c>
-      <c r="AC23">
-        <v>2.97</v>
-      </c>
-      <c r="AD23">
-        <v>1.3</v>
-      </c>
-      <c r="AE23">
-        <v>1.08</v>
-      </c>
-      <c r="AF23">
+      <c r="AE27">
+        <v>1.12</v>
+      </c>
+      <c r="AF27">
         <v>1.95</v>
       </c>
-      <c r="AG23">
+      <c r="AG27">
         <v>1.75</v>
       </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.22</v>
-      </c>
-      <c r="AK23">
-        <v>2.45</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
-        <v>-1</v>
-      </c>
-      <c r="AN23">
-        <v>-1</v>
-      </c>
-      <c r="AO23">
-        <v>-1</v>
-      </c>
-      <c r="AP23">
-        <v>-1</v>
-      </c>
-      <c r="AQ23">
-        <v>0</v>
-      </c>
-      <c r="AR23">
-        <v>0</v>
-      </c>
-      <c r="AS23">
-        <v>0</v>
-      </c>
-      <c r="AT23">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.23</v>
+      </c>
+      <c r="AK27">
+        <v>2.55</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-1</v>
+      </c>
+      <c r="AN27">
+        <v>-1</v>
+      </c>
+      <c r="AO27">
+        <v>-1</v>
+      </c>
+      <c r="AP27">
+        <v>-1</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
         <is>
           <t>2026-10-08 21:30:00</t>
         </is>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="O23">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P23">
-        <v>2.73</v>
+        <v>2.87</v>
       </c>
       <c r="Q23">
         <v>3.01</v>
       </c>
       <c r="R23">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S23">
         <v>1.44</v>
@@ -4079,7 +4079,7 @@
         <v>2.39</v>
       </c>
       <c r="U23">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="V23">
         <v>1.27</v>
@@ -4221,31 +4221,31 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O24">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P24">
         <v>2.2</v>
       </c>
       <c r="Q24">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="R24">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T24">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U24">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V24">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
         <v>1.07</v>
@@ -4260,10 +4260,10 @@
         <v>3.34</v>
       </c>
       <c r="AA24">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB24">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC24">
         <v>3.08</v>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU27"/>
+  <dimension ref="A1:AU31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G14">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-10-08 14:00:00</t>
+          <t>2026-10-08 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.57</v>
+        <v>2.65</v>
       </c>
       <c r="O16">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="P16">
-        <v>6</v>
+        <v>2.65</v>
       </c>
       <c r="Q16">
-        <v>2.22</v>
+        <v>3.52</v>
       </c>
       <c r="R16">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="S16">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="T16">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="U16">
-        <v>3.3</v>
+        <v>3.72</v>
       </c>
       <c r="V16">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W16">
+        <v>1.02</v>
+      </c>
+      <c r="X16">
+        <v>1.08</v>
+      </c>
+      <c r="Y16">
+        <v>1.55</v>
+      </c>
+      <c r="Z16">
+        <v>2.24</v>
+      </c>
+      <c r="AA16">
+        <v>2.62</v>
+      </c>
+      <c r="AB16">
+        <v>1.38</v>
+      </c>
+      <c r="AC16">
+        <v>5.2</v>
+      </c>
+      <c r="AD16">
+        <v>1.1</v>
+      </c>
+      <c r="AE16">
         <v>1.03</v>
       </c>
-      <c r="X16">
-        <v>1.06</v>
-      </c>
-      <c r="Y16">
-        <v>1.43</v>
-      </c>
-      <c r="Z16">
-        <v>2.46</v>
-      </c>
-      <c r="AA16">
-        <v>2.37</v>
-      </c>
-      <c r="AB16">
-        <v>1.53</v>
-      </c>
-      <c r="AC16">
-        <v>4.4</v>
-      </c>
-      <c r="AD16">
-        <v>1.14</v>
-      </c>
-      <c r="AE16">
-        <v>1.01</v>
-      </c>
       <c r="AF16">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="AG16">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AK16">
-        <v>2.12</v>
+        <v>1.36</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK18">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-10-08 14:30:00</t>
+          <t>2026-10-08 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,81 +3406,81 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="O19">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="P19">
-        <v>4.7</v>
+        <v>2.48</v>
       </c>
       <c r="Q19">
-        <v>2.41</v>
+        <v>2.95</v>
       </c>
       <c r="R19">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="S19">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="T19">
-        <v>2.24</v>
+        <v>2.84</v>
       </c>
       <c r="U19">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="V19">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X19">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="Z19">
-        <v>2.41</v>
+        <v>3.58</v>
       </c>
       <c r="AA19">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AB19">
+        <v>1.97</v>
+      </c>
+      <c r="AC19">
+        <v>2.78</v>
+      </c>
+      <c r="AD19">
+        <v>1.34</v>
+      </c>
+      <c r="AE19">
+        <v>1.1</v>
+      </c>
+      <c r="AF19">
+        <v>1.62</v>
+      </c>
+      <c r="AG19">
+        <v>2.15</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>1.3</v>
+      </c>
+      <c r="AK19">
         <v>1.5</v>
       </c>
-      <c r="AC19">
-        <v>4.85</v>
-      </c>
-      <c r="AD19">
-        <v>1.11</v>
-      </c>
-      <c r="AE19">
-        <v>1.02</v>
-      </c>
-      <c r="AF19">
-        <v>2.3</v>
-      </c>
-      <c r="AG19">
-        <v>1.54</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.26</v>
-      </c>
-      <c r="AK19">
-        <v>1.93</v>
-      </c>
       <c r="AL19">
         <v>0</v>
       </c>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-10-08 16:00:00</t>
+          <t>2026-10-08 14:30:00</t>
         </is>
       </c>
     </row>
@@ -3522,27 +3522,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Widad Témara</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R20">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V20">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z20">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC20">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AD20">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE20">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG20">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK20">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-10-08 16:00:00</t>
+          <t>2026-10-08 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G21">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N21">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-10-08 17:30:00</t>
+          <t>2026-10-08 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3848,27 +3848,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>4.1</v>
+        <v>1.75</v>
       </c>
       <c r="O22">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="P22">
-        <v>1.83</v>
+        <v>4.7</v>
       </c>
       <c r="Q22">
-        <v>4.2</v>
+        <v>2.41</v>
       </c>
       <c r="R22">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="S22">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="T22">
-        <v>3.08</v>
+        <v>2.24</v>
       </c>
       <c r="U22">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="V22">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="W22">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y22">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="Z22">
-        <v>3.9</v>
+        <v>2.41</v>
       </c>
       <c r="AA22">
-        <v>1.78</v>
+        <v>2.46</v>
       </c>
       <c r="AB22">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="AC22">
-        <v>2.9</v>
+        <v>4.85</v>
       </c>
       <c r="AD22">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AE22">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AG22">
-        <v>2.1</v>
+        <v>1.54</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK22">
-        <v>1.24</v>
+        <v>1.93</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-10-08 19:30:00</t>
+          <t>2026-10-08 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.22</v>
+        <v>1.4</v>
       </c>
       <c r="O23">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="P23">
-        <v>2.87</v>
+        <v>6.5</v>
       </c>
       <c r="Q23">
-        <v>3.01</v>
+        <v>1.83</v>
       </c>
       <c r="R23">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="S23">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="T23">
-        <v>2.39</v>
+        <v>3.22</v>
       </c>
       <c r="U23">
-        <v>3.32</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="W23">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="Z23">
-        <v>2.52</v>
+        <v>3.95</v>
       </c>
       <c r="AA23">
-        <v>2.36</v>
+        <v>1.72</v>
       </c>
       <c r="AB23">
-        <v>1.54</v>
+        <v>2.12</v>
       </c>
       <c r="AC23">
-        <v>4.3</v>
+        <v>2.66</v>
       </c>
       <c r="AD23">
+        <v>1.42</v>
+      </c>
+      <c r="AE23">
         <v>1.15</v>
       </c>
-      <c r="AE23">
-        <v>1.01</v>
-      </c>
       <c r="AF23">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AG23">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AK23">
-        <v>1.53</v>
+        <v>2.88</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-10-08 19:30:00</t>
+          <t>2026-10-08 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4174,27 +4174,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC24">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AK24">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-10-08 19:30:00</t>
+          <t>2026-10-08 17:00:00</t>
         </is>
       </c>
     </row>
@@ -4337,27 +4337,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G25">
@@ -4380,68 +4380,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N25">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y25">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC25">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK25">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-10-08 20:00:00</t>
+          <t>2026-10-08 17:30:00</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.57</v>
+        <v>4.1</v>
       </c>
       <c r="O26">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="P26">
-        <v>5.6</v>
+        <v>1.83</v>
       </c>
       <c r="Q26">
-        <v>2.03</v>
+        <v>4.2</v>
       </c>
       <c r="R26">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T26">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="U26">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="V26">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W26">
+        <v>1.1</v>
+      </c>
+      <c r="X26">
+        <v>1.01</v>
+      </c>
+      <c r="Y26">
+        <v>1.21</v>
+      </c>
+      <c r="Z26">
+        <v>3.9</v>
+      </c>
+      <c r="AA26">
+        <v>1.78</v>
+      </c>
+      <c r="AB26">
+        <v>2.07</v>
+      </c>
+      <c r="AC26">
+        <v>2.9</v>
+      </c>
+      <c r="AD26">
+        <v>1.35</v>
+      </c>
+      <c r="AE26">
         <v>1.11</v>
       </c>
-      <c r="X26">
-        <v>1.03</v>
-      </c>
-      <c r="Y26">
-        <v>1.17</v>
-      </c>
-      <c r="Z26">
-        <v>4.4</v>
-      </c>
-      <c r="AA26">
+      <c r="AF26">
         <v>1.67</v>
       </c>
-      <c r="AB26">
-        <v>2.15</v>
-      </c>
-      <c r="AC26">
-        <v>2.49</v>
-      </c>
-      <c r="AD26">
-        <v>1.49</v>
-      </c>
-      <c r="AE26">
-        <v>1.14</v>
-      </c>
-      <c r="AF26">
-        <v>1.73</v>
-      </c>
       <c r="AG26">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.2</v>
       </c>
       <c r="AK26">
-        <v>2.32</v>
+        <v>1.24</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-10-08 21:30:00</t>
+          <t>2026-10-08 19:30:00</t>
         </is>
       </c>
     </row>
@@ -4663,156 +4663,808 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27">
+        <v>2.22</v>
+      </c>
+      <c r="O27">
+        <v>3.1</v>
+      </c>
+      <c r="P27">
+        <v>2.87</v>
+      </c>
+      <c r="Q27">
+        <v>3.01</v>
+      </c>
+      <c r="R27">
+        <v>1.91</v>
+      </c>
+      <c r="S27">
+        <v>1.44</v>
+      </c>
+      <c r="T27">
+        <v>2.39</v>
+      </c>
+      <c r="U27">
+        <v>3.32</v>
+      </c>
+      <c r="V27">
+        <v>1.27</v>
+      </c>
+      <c r="W27">
+        <v>1.01</v>
+      </c>
+      <c r="X27">
+        <v>1.05</v>
+      </c>
+      <c r="Y27">
+        <v>1.41</v>
+      </c>
+      <c r="Z27">
+        <v>2.52</v>
+      </c>
+      <c r="AA27">
+        <v>2.36</v>
+      </c>
+      <c r="AB27">
+        <v>1.54</v>
+      </c>
+      <c r="AC27">
+        <v>4.3</v>
+      </c>
+      <c r="AD27">
+        <v>1.15</v>
+      </c>
+      <c r="AE27">
+        <v>1.01</v>
+      </c>
+      <c r="AF27">
+        <v>1.98</v>
+      </c>
+      <c r="AG27">
+        <v>1.72</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.36</v>
+      </c>
+      <c r="AK27">
+        <v>1.53</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-1</v>
+      </c>
+      <c r="AN27">
+        <v>-1</v>
+      </c>
+      <c r="AO27">
+        <v>-1</v>
+      </c>
+      <c r="AP27">
+        <v>-1</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N28">
+        <v>3.05</v>
+      </c>
+      <c r="O28">
+        <v>3.4</v>
+      </c>
+      <c r="P28">
+        <v>2.2</v>
+      </c>
+      <c r="Q28">
+        <v>3.69</v>
+      </c>
+      <c r="R28">
+        <v>2.25</v>
+      </c>
+      <c r="S28">
+        <v>1.35</v>
+      </c>
+      <c r="T28">
+        <v>2.9</v>
+      </c>
+      <c r="U28">
+        <v>2.7</v>
+      </c>
+      <c r="V28">
+        <v>1.4</v>
+      </c>
+      <c r="W28">
+        <v>1.07</v>
+      </c>
+      <c r="X28">
+        <v>1</v>
+      </c>
+      <c r="Y28">
+        <v>1.24</v>
+      </c>
+      <c r="Z28">
+        <v>3.34</v>
+      </c>
+      <c r="AA28">
+        <v>1.9</v>
+      </c>
+      <c r="AB28">
+        <v>1.9</v>
+      </c>
+      <c r="AC28">
+        <v>3.08</v>
+      </c>
+      <c r="AD28">
+        <v>1.28</v>
+      </c>
+      <c r="AE28">
+        <v>1.07</v>
+      </c>
+      <c r="AF28">
+        <v>1.69</v>
+      </c>
+      <c r="AG28">
+        <v>2.05</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>1.57</v>
+      </c>
+      <c r="AK28">
+        <v>1.36</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>-1</v>
+      </c>
+      <c r="AN28">
+        <v>-1</v>
+      </c>
+      <c r="AO28">
+        <v>-1</v>
+      </c>
+      <c r="AP28">
+        <v>-1</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N29">
+        <v>2.05</v>
+      </c>
+      <c r="O29">
+        <v>3.35</v>
+      </c>
+      <c r="P29">
+        <v>3.6</v>
+      </c>
+      <c r="Q29">
+        <v>2.65</v>
+      </c>
+      <c r="R29">
+        <v>2.22</v>
+      </c>
+      <c r="S29">
+        <v>1.43</v>
+      </c>
+      <c r="T29">
+        <v>2.57</v>
+      </c>
+      <c r="U29">
+        <v>2.88</v>
+      </c>
+      <c r="V29">
+        <v>1.4</v>
+      </c>
+      <c r="W29">
+        <v>1.04</v>
+      </c>
+      <c r="X29">
+        <v>1.04</v>
+      </c>
+      <c r="Y29">
+        <v>1.32</v>
+      </c>
+      <c r="Z29">
+        <v>2.97</v>
+      </c>
+      <c r="AA29">
+        <v>2.04</v>
+      </c>
+      <c r="AB29">
+        <v>1.83</v>
+      </c>
+      <c r="AC29">
+        <v>3.6</v>
+      </c>
+      <c r="AD29">
+        <v>1.26</v>
+      </c>
+      <c r="AE29">
+        <v>1.06</v>
+      </c>
+      <c r="AF29">
+        <v>1.8</v>
+      </c>
+      <c r="AG29">
+        <v>1.92</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>1.24</v>
+      </c>
+      <c r="AK29">
+        <v>1.72</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>-1</v>
+      </c>
+      <c r="AN29">
+        <v>-1</v>
+      </c>
+      <c r="AO29">
+        <v>-1</v>
+      </c>
+      <c r="AP29">
+        <v>-1</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>2026-10-08 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N30">
+        <v>1.57</v>
+      </c>
+      <c r="O30">
+        <v>4.15</v>
+      </c>
+      <c r="P30">
+        <v>5.6</v>
+      </c>
+      <c r="Q30">
+        <v>2.03</v>
+      </c>
+      <c r="R30">
+        <v>2.54</v>
+      </c>
+      <c r="S30">
+        <v>1.29</v>
+      </c>
+      <c r="T30">
+        <v>3.22</v>
+      </c>
+      <c r="U30">
+        <v>2.29</v>
+      </c>
+      <c r="V30">
+        <v>1.5</v>
+      </c>
+      <c r="W30">
+        <v>1.11</v>
+      </c>
+      <c r="X30">
+        <v>1.03</v>
+      </c>
+      <c r="Y30">
+        <v>1.17</v>
+      </c>
+      <c r="Z30">
+        <v>4.4</v>
+      </c>
+      <c r="AA30">
+        <v>1.67</v>
+      </c>
+      <c r="AB30">
+        <v>2.15</v>
+      </c>
+      <c r="AC30">
+        <v>2.49</v>
+      </c>
+      <c r="AD30">
+        <v>1.49</v>
+      </c>
+      <c r="AE30">
+        <v>1.14</v>
+      </c>
+      <c r="AF30">
+        <v>1.73</v>
+      </c>
+      <c r="AG30">
+        <v>2</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>1.2</v>
+      </c>
+      <c r="AK30">
+        <v>2.34</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>-1</v>
+      </c>
+      <c r="AN30">
+        <v>-1</v>
+      </c>
+      <c r="AO30">
+        <v>-1</v>
+      </c>
+      <c r="AP30">
+        <v>-1</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>2026-10-08 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>Fluminense</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
       </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N27">
-        <v>1.48</v>
-      </c>
-      <c r="O27">
-        <v>4.4</v>
-      </c>
-      <c r="P27">
-        <v>6.5</v>
-      </c>
-      <c r="Q27">
+      <c r="N31">
+        <v>1.5</v>
+      </c>
+      <c r="O31">
+        <v>4.33</v>
+      </c>
+      <c r="P31">
+        <v>6</v>
+      </c>
+      <c r="Q31">
         <v>2.01</v>
       </c>
-      <c r="R27">
+      <c r="R31">
         <v>2.25</v>
       </c>
-      <c r="S27">
+      <c r="S31">
         <v>1.33</v>
       </c>
-      <c r="T27">
+      <c r="T31">
         <v>2.97</v>
       </c>
-      <c r="U27">
+      <c r="U31">
         <v>2.55</v>
       </c>
-      <c r="V27">
+      <c r="V31">
         <v>1.42</v>
       </c>
-      <c r="W27">
+      <c r="W31">
         <v>1.08</v>
       </c>
-      <c r="X27">
+      <c r="X31">
         <v>1</v>
       </c>
-      <c r="Y27">
+      <c r="Y31">
         <v>1.24</v>
       </c>
-      <c r="Z27">
+      <c r="Z31">
         <v>3.34</v>
       </c>
-      <c r="AA27">
+      <c r="AA31">
         <v>1.9</v>
       </c>
-      <c r="AB27">
+      <c r="AB31">
         <v>1.94</v>
       </c>
-      <c r="AC27">
+      <c r="AC31">
         <v>2.97</v>
       </c>
-      <c r="AD27">
+      <c r="AD31">
         <v>1.35</v>
       </c>
-      <c r="AE27">
+      <c r="AE31">
         <v>1.12</v>
       </c>
-      <c r="AF27">
+      <c r="AF31">
         <v>1.95</v>
       </c>
-      <c r="AG27">
+      <c r="AG31">
         <v>1.75</v>
       </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
         <v>1.23</v>
       </c>
-      <c r="AK27">
+      <c r="AK31">
         <v>2.55</v>
       </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>-1</v>
-      </c>
-      <c r="AN27">
-        <v>-1</v>
-      </c>
-      <c r="AO27">
-        <v>-1</v>
-      </c>
-      <c r="AP27">
-        <v>-1</v>
-      </c>
-      <c r="AQ27">
-        <v>0</v>
-      </c>
-      <c r="AR27">
-        <v>0</v>
-      </c>
-      <c r="AS27">
-        <v>0</v>
-      </c>
-      <c r="AT27">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>-1</v>
+      </c>
+      <c r="AN31">
+        <v>-1</v>
+      </c>
+      <c r="AO31">
+        <v>-1</v>
+      </c>
+      <c r="AP31">
+        <v>-1</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
         <is>
           <t>2026-10-08 21:30:00</t>
         </is>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -2932,28 +2932,28 @@
         <v>1.82</v>
       </c>
       <c r="S16">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="T16">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U16">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="V16">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W16">
         <v>1.02</v>
       </c>
       <c r="X16">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y16">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Z16">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="AA16">
         <v>2.62</v>
@@ -2962,10 +2962,10 @@
         <v>1.38</v>
       </c>
       <c r="AC16">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AD16">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AE16">
         <v>1.03</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="O17">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="Q17">
         <v>2.22</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3952,7 +3952,7 @@
         <v>2.3</v>
       </c>
       <c r="AG22">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q24">
         <v>0</v>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G9">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-10-08 11:45:00</t>
+          <t>2026-10-08 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-10-08 12:00:00</t>
+          <t>2026-10-08 12:15:00</t>
         </is>
       </c>
     </row>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>6.82</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2630,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -2959,7 +2959,7 @@
         <v>2.62</v>
       </c>
       <c r="AB16">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AC16">
         <v>5.4</v>
@@ -3080,43 +3080,43 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="O17">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="Q17">
+        <v>2.38</v>
+      </c>
+      <c r="R17">
+        <v>1.87</v>
+      </c>
+      <c r="S17">
+        <v>1.56</v>
+      </c>
+      <c r="T17">
         <v>2.22</v>
       </c>
-      <c r="R17">
-        <v>1.95</v>
-      </c>
-      <c r="S17">
-        <v>1.5</v>
-      </c>
-      <c r="T17">
-        <v>2.29</v>
-      </c>
       <c r="U17">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="V17">
         <v>1.25</v>
       </c>
       <c r="W17">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y17">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Z17">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AA17">
         <v>2.37</v>
@@ -3125,19 +3125,19 @@
         <v>1.53</v>
       </c>
       <c r="AC17">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD17">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF17">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="AG17">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK17">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3415,28 +3415,28 @@
         <v>2.48</v>
       </c>
       <c r="Q19">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="R19">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
         <v>1.33</v>
       </c>
       <c r="T19">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="U19">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
         <v>1.09</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y19">
         <v>1.25</v>
@@ -3457,7 +3457,7 @@
         <v>1.34</v>
       </c>
       <c r="AE19">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF19">
         <v>1.62</v>
@@ -3479,7 +3479,7 @@
         <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3946,7 +3946,7 @@
         <v>1.11</v>
       </c>
       <c r="AE22">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF22">
         <v>2.3</v>
@@ -4550,22 +4550,22 @@
         <v>4.1</v>
       </c>
       <c r="O26">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P26">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q26">
         <v>4.2</v>
       </c>
       <c r="R26">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S26">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T26">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="U26">
         <v>2.62</v>
@@ -4574,7 +4574,7 @@
         <v>1.47</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4583,13 +4583,13 @@
         <v>1.21</v>
       </c>
       <c r="Z26">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AA26">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AB26">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC26">
         <v>2.9</v>
@@ -4713,22 +4713,22 @@
         <v>2.22</v>
       </c>
       <c r="O27">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="P27">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q27">
         <v>3.01</v>
       </c>
       <c r="R27">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S27">
         <v>1.44</v>
       </c>
       <c r="T27">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="U27">
         <v>3.32</v>
@@ -4746,7 +4746,7 @@
         <v>1.41</v>
       </c>
       <c r="Z27">
-        <v>2.52</v>
+        <v>2.77</v>
       </c>
       <c r="AA27">
         <v>2.36</v>
@@ -4761,7 +4761,7 @@
         <v>1.15</v>
       </c>
       <c r="AE27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF27">
         <v>1.98</v>
@@ -4873,16 +4873,16 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O28">
         <v>3.4</v>
       </c>
       <c r="P28">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="Q28">
-        <v>3.69</v>
+        <v>3.75</v>
       </c>
       <c r="R28">
         <v>2.25</v>
@@ -4918,10 +4918,10 @@
         <v>1.9</v>
       </c>
       <c r="AC28">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD28">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE28">
         <v>1.07</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AK28">
         <v>1.36</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O29">
         <v>3.35</v>
@@ -5048,7 +5048,7 @@
         <v>2.65</v>
       </c>
       <c r="R29">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="S29">
         <v>1.43</v>
@@ -5069,19 +5069,19 @@
         <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z29">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AA29">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AB29">
         <v>1.83</v>
       </c>
       <c r="AC29">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AD29">
         <v>1.26</v>
@@ -5093,7 +5093,7 @@
         <v>1.8</v>
       </c>
       <c r="AG29">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5208,16 +5208,16 @@
         <v>5.6</v>
       </c>
       <c r="Q30">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="R30">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="S30">
         <v>1.29</v>
       </c>
       <c r="T30">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="U30">
         <v>2.29</v>
@@ -5226,10 +5226,10 @@
         <v>1.5</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
         <v>1.17</v>
@@ -5247,7 +5247,7 @@
         <v>2.49</v>
       </c>
       <c r="AD30">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AE30">
         <v>1.14</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AK30">
         <v>2.34</v>
@@ -5371,10 +5371,10 @@
         <v>6</v>
       </c>
       <c r="Q31">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="R31">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S31">
         <v>1.33</v>
@@ -5383,34 +5383,34 @@
         <v>2.97</v>
       </c>
       <c r="U31">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="V31">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W31">
         <v>1.08</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z31">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AA31">
         <v>1.9</v>
       </c>
       <c r="AB31">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC31">
-        <v>2.97</v>
+        <v>3.21</v>
       </c>
       <c r="AD31">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE31">
         <v>1.12</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AL31">
         <v>0</v>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G2">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.6</v>
+        <v>4.37</v>
       </c>
       <c r="O2">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="P2">
-        <v>4.88</v>
+        <v>1.78</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="AB2">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G3">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>4.37</v>
+        <v>1.6</v>
       </c>
       <c r="O3">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="P3">
-        <v>1.78</v>
+        <v>4.88</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="AB3">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="O16">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="P16">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="Q16">
-        <v>3.52</v>
+        <v>4.6</v>
       </c>
       <c r="R16">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="S16">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="T16">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="U16">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="V16">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W16">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X16">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y16">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="Z16">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AA16">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AB16">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AC16">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AD16">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AE16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF16">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AG16">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.32</v>
       </c>
       <c r="AK16">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="O17">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="P17">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="Q17">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="R17">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="S17">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="T17">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="U17">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="V17">
         <v>1.25</v>
       </c>
       <c r="W17">
+        <v>1.03</v>
+      </c>
+      <c r="X17">
+        <v>1.08</v>
+      </c>
+      <c r="Y17">
+        <v>1.52</v>
+      </c>
+      <c r="Z17">
+        <v>2.44</v>
+      </c>
+      <c r="AA17">
+        <v>2.64</v>
+      </c>
+      <c r="AB17">
+        <v>1.44</v>
+      </c>
+      <c r="AC17">
+        <v>5</v>
+      </c>
+      <c r="AD17">
+        <v>1.17</v>
+      </c>
+      <c r="AE17">
         <v>1.04</v>
       </c>
-      <c r="X17">
-        <v>1.07</v>
-      </c>
-      <c r="Y17">
-        <v>1.42</v>
-      </c>
-      <c r="Z17">
-        <v>2.49</v>
-      </c>
-      <c r="AA17">
-        <v>2.37</v>
-      </c>
-      <c r="AB17">
-        <v>1.53</v>
-      </c>
-      <c r="AC17">
-        <v>4.2</v>
-      </c>
-      <c r="AD17">
-        <v>1.15</v>
-      </c>
-      <c r="AE17">
-        <v>1.02</v>
-      </c>
       <c r="AF17">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AG17">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AK17">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
+        <v>1.36</v>
+      </c>
+      <c r="O20">
+        <v>4.4</v>
+      </c>
+      <c r="P20">
+        <v>8.6</v>
+      </c>
+      <c r="Q20">
+        <v>2.13</v>
+      </c>
+      <c r="R20">
+        <v>1.92</v>
+      </c>
+      <c r="S20">
+        <v>1.5</v>
+      </c>
+      <c r="T20">
+        <v>2.29</v>
+      </c>
+      <c r="U20">
+        <v>2.99</v>
+      </c>
+      <c r="V20">
         <v>1.3</v>
       </c>
-      <c r="O20">
-        <v>4.33</v>
-      </c>
-      <c r="P20">
-        <v>8.5</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA20">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AB20">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="O21">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="P21">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3946,7 +3946,7 @@
         <v>1.11</v>
       </c>
       <c r="AE22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF22">
         <v>2.3</v>
@@ -4067,10 +4067,10 @@
         <v>6.5</v>
       </c>
       <c r="Q23">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="R23">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="S23">
         <v>1.28</v>
@@ -4079,16 +4079,16 @@
         <v>3.22</v>
       </c>
       <c r="U23">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V23">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
         <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
         <v>1.17</v>
@@ -4131,7 +4131,7 @@
         <v>1.17</v>
       </c>
       <c r="AK23">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="O24">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="P24">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25">
@@ -4586,7 +4586,7 @@
         <v>3.58</v>
       </c>
       <c r="AA26">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB26">
         <v>2.05</v>
@@ -4620,7 +4620,7 @@
         <v>1.2</v>
       </c>
       <c r="AK26">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5048,7 +5048,7 @@
         <v>2.65</v>
       </c>
       <c r="R29">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
         <v>1.43</v>
@@ -5365,10 +5365,10 @@
         <v>1.5</v>
       </c>
       <c r="O31">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P31">
-        <v>6</v>
+        <v>6.65</v>
       </c>
       <c r="Q31">
         <v>2</v>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Widad Témara</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.36</v>
+        <v>2.29</v>
       </c>
       <c r="O20">
-        <v>4.4</v>
+        <v>2.85</v>
       </c>
       <c r="P20">
-        <v>8.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q20">
-        <v>2.13</v>
+        <v>3.34</v>
       </c>
       <c r="R20">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="S20">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T20">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="U20">
-        <v>2.99</v>
+        <v>3.28</v>
       </c>
       <c r="V20">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X20">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y20">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="Z20">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="AA20">
-        <v>2.03</v>
+        <v>2.44</v>
       </c>
       <c r="AB20">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="AC20">
-        <v>3.34</v>
+        <v>4.55</v>
       </c>
       <c r="AD20">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AE20">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AF20">
-        <v>2.21</v>
+        <v>2.01</v>
       </c>
       <c r="AG20">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AK20">
-        <v>2.34</v>
+        <v>1.41</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Widad Témara</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
+        <v>1.36</v>
+      </c>
+      <c r="O21">
+        <v>4.4</v>
+      </c>
+      <c r="P21">
+        <v>8.6</v>
+      </c>
+      <c r="Q21">
+        <v>2.13</v>
+      </c>
+      <c r="R21">
+        <v>1.92</v>
+      </c>
+      <c r="S21">
+        <v>1.5</v>
+      </c>
+      <c r="T21">
         <v>2.29</v>
       </c>
-      <c r="O21">
-        <v>2.85</v>
-      </c>
-      <c r="P21">
-        <v>3.45</v>
-      </c>
-      <c r="Q21">
+      <c r="U21">
+        <v>2.99</v>
+      </c>
+      <c r="V21">
+        <v>1.3</v>
+      </c>
+      <c r="W21">
+        <v>1.05</v>
+      </c>
+      <c r="X21">
+        <v>1.05</v>
+      </c>
+      <c r="Y21">
+        <v>1.32</v>
+      </c>
+      <c r="Z21">
+        <v>2.88</v>
+      </c>
+      <c r="AA21">
+        <v>2.03</v>
+      </c>
+      <c r="AB21">
+        <v>1.67</v>
+      </c>
+      <c r="AC21">
         <v>3.34</v>
       </c>
-      <c r="R21">
-        <v>1.78</v>
-      </c>
-      <c r="S21">
-        <v>1.55</v>
-      </c>
-      <c r="T21">
-        <v>2.25</v>
-      </c>
-      <c r="U21">
-        <v>3.28</v>
-      </c>
-      <c r="V21">
-        <v>1.25</v>
-      </c>
-      <c r="W21">
-        <v>1.03</v>
-      </c>
-      <c r="X21">
-        <v>1.07</v>
-      </c>
-      <c r="Y21">
-        <v>1.44</v>
-      </c>
-      <c r="Z21">
-        <v>2.43</v>
-      </c>
-      <c r="AA21">
-        <v>2.44</v>
-      </c>
-      <c r="AB21">
-        <v>1.47</v>
-      </c>
-      <c r="AC21">
-        <v>4.55</v>
-      </c>
       <c r="AD21">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AE21">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AF21">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="AG21">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>1.41</v>
+        <v>2.34</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4713,7 +4713,7 @@
         <v>2.22</v>
       </c>
       <c r="O27">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
         <v>2.8</v>
@@ -4722,7 +4722,7 @@
         <v>3.01</v>
       </c>
       <c r="R27">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S27">
         <v>1.44</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="Q28">
         <v>3.75</v>
@@ -4918,7 +4918,7 @@
         <v>1.9</v>
       </c>
       <c r="AC28">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AD28">
         <v>1.33</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AK28">
         <v>1.36</v>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -2428,61 +2428,61 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="O13">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="P13">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q13">
-        <v>4.44</v>
+        <v>4.32</v>
       </c>
       <c r="R13">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="S13">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T13">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="U13">
-        <v>3.34</v>
+        <v>3.18</v>
       </c>
       <c r="V13">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="W13">
+        <v>1.03</v>
+      </c>
+      <c r="X13">
+        <v>1.06</v>
+      </c>
+      <c r="Y13">
+        <v>1.41</v>
+      </c>
+      <c r="Z13">
+        <v>2.62</v>
+      </c>
+      <c r="AA13">
+        <v>2.21</v>
+      </c>
+      <c r="AB13">
+        <v>1.53</v>
+      </c>
+      <c r="AC13">
+        <v>4.05</v>
+      </c>
+      <c r="AD13">
+        <v>1.17</v>
+      </c>
+      <c r="AE13">
         <v>1.02</v>
       </c>
-      <c r="X13">
-        <v>1.07</v>
-      </c>
-      <c r="Y13">
-        <v>1.45</v>
-      </c>
-      <c r="Z13">
-        <v>2.49</v>
-      </c>
-      <c r="AA13">
-        <v>2.35</v>
-      </c>
-      <c r="AB13">
-        <v>1.47</v>
-      </c>
-      <c r="AC13">
-        <v>4.4</v>
-      </c>
-      <c r="AD13">
-        <v>1.14</v>
-      </c>
-      <c r="AE13">
-        <v>1.01</v>
-      </c>
       <c r="AF13">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG13">
         <v>1.7</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AK13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>3.45</v>
       </c>
       <c r="Q20">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="R20">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="S20">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="T20">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="U20">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="V20">
         <v>1.25</v>
       </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y20">
         <v>1.44</v>
       </c>
       <c r="Z20">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AA20">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AB20">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC20">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="AD20">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE20">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF20">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG20">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK20">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>8.6</v>
       </c>
       <c r="Q21">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="R21">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="S21">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="T21">
-        <v>2.29</v>
+        <v>2.71</v>
       </c>
       <c r="U21">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="V21">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z21">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA21">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB21">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC21">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD21">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE21">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AG21">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="O24">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="P24">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q24">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="R24">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S24">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="T24">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="U24">
-        <v>3.52</v>
+        <v>4</v>
       </c>
       <c r="V24">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X24">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y24">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Z24">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="AA24">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AB24">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AC24">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AD24">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE24">
         <v>1.01</v>
       </c>
       <c r="AF24">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AG24">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK24">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AL24">
         <v>0</v>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>4.37</v>
+        <v>4.3</v>
       </c>
       <c r="O2">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="O10">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P10">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="O15">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="P15">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2917,25 +2917,25 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O16">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P16">
         <v>2.33</v>
       </c>
       <c r="Q16">
-        <v>4.6</v>
+        <v>4.03</v>
       </c>
       <c r="R16">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S16">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="T16">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="U16">
         <v>3.58</v>
@@ -2947,22 +2947,22 @@
         <v>1.04</v>
       </c>
       <c r="X16">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y16">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z16">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="AA16">
-        <v>2.52</v>
+        <v>2.61</v>
       </c>
       <c r="AB16">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AC16">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AD16">
         <v>1.14</v>
@@ -2971,10 +2971,10 @@
         <v>1.01</v>
       </c>
       <c r="AF16">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AG16">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK16">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,31 +3080,31 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="O17">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P17">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Q17">
-        <v>2.67</v>
+        <v>2.47</v>
       </c>
       <c r="R17">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="S17">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="T17">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="U17">
         <v>3.5</v>
       </c>
       <c r="V17">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W17">
         <v>1.03</v>
@@ -3113,16 +3113,16 @@
         <v>1.08</v>
       </c>
       <c r="Y17">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z17">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="AA17">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="AB17">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AC17">
         <v>5</v>
@@ -3131,13 +3131,13 @@
         <v>1.17</v>
       </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF17">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AG17">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK17">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3415,22 +3415,22 @@
         <v>2.48</v>
       </c>
       <c r="Q19">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R19">
         <v>2.25</v>
       </c>
       <c r="S19">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T19">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U19">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V19">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W19">
         <v>1.09</v>
@@ -3457,13 +3457,13 @@
         <v>1.34</v>
       </c>
       <c r="AE19">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF19">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG19">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="O22">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P22">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q22">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="R22">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="S22">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="T22">
         <v>2.24</v>
       </c>
       <c r="U22">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="V22">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W22">
         <v>1.04</v>
       </c>
       <c r="X22">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y22">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="Z22">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="AA22">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="AB22">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AC22">
-        <v>4.85</v>
+        <v>5.3</v>
       </c>
       <c r="AD22">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE22">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF22">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AG22">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AK22">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4740,13 +4740,13 @@
         <v>1.01</v>
       </c>
       <c r="X27">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y27">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z27">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AA27">
         <v>2.36</v>
@@ -4761,13 +4761,13 @@
         <v>1.15</v>
       </c>
       <c r="AE27">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF27">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG27">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="O28">
         <v>3.3</v>
@@ -4903,13 +4903,13 @@
         <v>1.07</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z28">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA28">
         <v>1.9</v>
@@ -4918,19 +4918,19 @@
         <v>1.9</v>
       </c>
       <c r="AC28">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AD28">
         <v>1.33</v>
       </c>
       <c r="AE28">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF28">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG28">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -4067,10 +4067,10 @@
         <v>6.5</v>
       </c>
       <c r="Q23">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R23">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="S23">
         <v>1.28</v>
@@ -4079,13 +4079,13 @@
         <v>3.22</v>
       </c>
       <c r="U23">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
         <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X23">
         <v>1.02</v>
@@ -4103,7 +4103,7 @@
         <v>2.12</v>
       </c>
       <c r="AC23">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AD23">
         <v>1.42</v>
@@ -4115,7 +4115,7 @@
         <v>1.9</v>
       </c>
       <c r="AG23">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK23">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>4.1</v>
+        <v>4.12</v>
       </c>
       <c r="O26">
         <v>3.8</v>
@@ -4577,34 +4577,34 @@
         <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="AA26">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB26">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AC26">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD26">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE26">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF26">
         <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
         <v>1.22</v>
@@ -5036,22 +5036,22 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="O29">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="P29">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="Q29">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="S29">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T29">
         <v>2.57</v>
@@ -5066,13 +5066,13 @@
         <v>1.04</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y29">
         <v>1.3</v>
       </c>
       <c r="Z29">
-        <v>3.25</v>
+        <v>3.39</v>
       </c>
       <c r="AA29">
         <v>2</v>
@@ -5081,19 +5081,19 @@
         <v>1.83</v>
       </c>
       <c r="AC29">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD29">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE29">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF29">
         <v>1.8</v>
       </c>
       <c r="AG29">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>1.57</v>
       </c>
       <c r="O30">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P30">
         <v>5.6</v>
@@ -5229,25 +5229,25 @@
         <v>1.1</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
         <v>1.17</v>
       </c>
       <c r="Z30">
-        <v>4.4</v>
+        <v>4.48</v>
       </c>
       <c r="AA30">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB30">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC30">
         <v>2.49</v>
       </c>
       <c r="AD30">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AE30">
         <v>1.14</v>
@@ -5365,10 +5365,10 @@
         <v>1.5</v>
       </c>
       <c r="O31">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P31">
-        <v>6.65</v>
+        <v>5.8</v>
       </c>
       <c r="Q31">
         <v>2</v>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P2">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA2">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="AB2">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,34 +807,34 @@
         <v>4.88</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA3">
         <v>2</v>
@@ -843,19 +843,19 @@
         <v>1.8</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="O9">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P9">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="O10">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="Q10">
         <v>2.73</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="O14">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="P14">
-        <v>6.82</v>
+        <v>5.39</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA14">
         <v>2</v>
       </c>
       <c r="AB14">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
+        <v>2.63</v>
+      </c>
+      <c r="O15">
         <v>2.8</v>
       </c>
-      <c r="O15">
-        <v>2.62</v>
-      </c>
       <c r="P15">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA15">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AB15">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O16">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P16">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="Q16">
         <v>4.03</v>
@@ -2938,13 +2938,13 @@
         <v>2.2</v>
       </c>
       <c r="U16">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="V16">
         <v>1.21</v>
       </c>
       <c r="W16">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
         <v>1.07</v>
@@ -2953,7 +2953,7 @@
         <v>1.5</v>
       </c>
       <c r="Z16">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AA16">
         <v>2.61</v>
@@ -2965,16 +2965,16 @@
         <v>4.9</v>
       </c>
       <c r="AD16">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AE16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF16">
         <v>2.09</v>
       </c>
       <c r="AG16">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK16">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,25 +3080,25 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="O17">
         <v>3</v>
       </c>
       <c r="P17">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q17">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="R17">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S17">
         <v>1.58</v>
       </c>
       <c r="T17">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="U17">
         <v>3.5</v>
@@ -3119,16 +3119,16 @@
         <v>2.48</v>
       </c>
       <c r="AA17">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AB17">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AC17">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AD17">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE17">
         <v>1</v>
@@ -3153,7 +3153,7 @@
         <v>1.11</v>
       </c>
       <c r="AK17">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O18">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3415,7 +3415,7 @@
         <v>2.48</v>
       </c>
       <c r="Q19">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R19">
         <v>2.25</v>
@@ -3430,7 +3430,7 @@
         <v>2.45</v>
       </c>
       <c r="V19">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W19">
         <v>1.09</v>
@@ -3457,13 +3457,13 @@
         <v>1.34</v>
       </c>
       <c r="AE19">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF19">
         <v>1.61</v>
       </c>
       <c r="AG19">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,22 +3569,22 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="O20">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="P20">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
       </c>
       <c r="R20">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="S20">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T20">
         <v>2.55</v>
@@ -3602,16 +3602,16 @@
         <v>1.06</v>
       </c>
       <c r="Y20">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z20">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="AA20">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AB20">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AC20">
         <v>4.8</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="O21">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="P21">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Q21">
         <v>1.85</v>
@@ -3747,7 +3747,7 @@
         <v>2.2</v>
       </c>
       <c r="S21">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="T21">
         <v>2.71</v>
@@ -3759,7 +3759,7 @@
         <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
         <v>1.04</v>
@@ -3771,7 +3771,7 @@
         <v>2.92</v>
       </c>
       <c r="AA21">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AB21">
         <v>1.7</v>
@@ -3786,10 +3786,10 @@
         <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AG21">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK21">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="O22">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P22">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q22">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="R22">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S22">
         <v>1.62</v>
@@ -3925,7 +3925,7 @@
         <v>1.04</v>
       </c>
       <c r="X22">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y22">
         <v>1.58</v>
@@ -3946,7 +3946,7 @@
         <v>1.14</v>
       </c>
       <c r="AE22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF22">
         <v>2.28</v>
@@ -3968,7 +3968,7 @@
         <v>1.14</v>
       </c>
       <c r="AK22">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4236,10 +4236,10 @@
         <v>1.83</v>
       </c>
       <c r="S24">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="T24">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="U24">
         <v>4</v>
@@ -4257,7 +4257,7 @@
         <v>1.51</v>
       </c>
       <c r="Z24">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AA24">
         <v>2.59</v>
@@ -4275,7 +4275,7 @@
         <v>1.01</v>
       </c>
       <c r="AF24">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AG24">
         <v>1.65</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="O27">
         <v>3.1</v>
@@ -4722,7 +4722,7 @@
         <v>3.01</v>
       </c>
       <c r="R27">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S27">
         <v>1.44</v>
@@ -4761,13 +4761,13 @@
         <v>1.15</v>
       </c>
       <c r="AE27">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF27">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG27">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,16 +4873,16 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.05</v>
+        <v>2.53</v>
       </c>
       <c r="O28">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P28">
         <v>2.15</v>
       </c>
       <c r="Q28">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="R28">
         <v>2.25</v>
@@ -4924,7 +4924,7 @@
         <v>1.33</v>
       </c>
       <c r="AE28">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF28">
         <v>1.67</v>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,58 +2591,58 @@
         </is>
       </c>
       <c r="N14">
+        <v>2.63</v>
+      </c>
+      <c r="O14">
+        <v>2.8</v>
+      </c>
+      <c r="P14">
+        <v>2.55</v>
+      </c>
+      <c r="Q14">
+        <v>3.5</v>
+      </c>
+      <c r="R14">
+        <v>1.91</v>
+      </c>
+      <c r="S14">
         <v>1.5</v>
       </c>
-      <c r="O14">
-        <v>3.6</v>
-      </c>
-      <c r="P14">
-        <v>5.39</v>
-      </c>
-      <c r="Q14">
-        <v>2</v>
-      </c>
-      <c r="R14">
-        <v>2.2</v>
-      </c>
-      <c r="S14">
-        <v>1.36</v>
-      </c>
       <c r="T14">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="U14">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="V14">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y14">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="Z14">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA14">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AB14">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AC14">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD14">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AE14">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF14">
         <v>2.1</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK14">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,58 +2754,58 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.63</v>
+        <v>1.5</v>
       </c>
       <c r="O15">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
-        <v>2.55</v>
+        <v>5.39</v>
       </c>
       <c r="Q15">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="R15">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="T15">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="U15">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="V15">
+        <v>1.36</v>
+      </c>
+      <c r="W15">
+        <v>1.05</v>
+      </c>
+      <c r="X15">
+        <v>1.02</v>
+      </c>
+      <c r="Y15">
+        <v>1.29</v>
+      </c>
+      <c r="Z15">
+        <v>3.3</v>
+      </c>
+      <c r="AA15">
+        <v>2</v>
+      </c>
+      <c r="AB15">
+        <v>1.75</v>
+      </c>
+      <c r="AC15">
+        <v>3.6</v>
+      </c>
+      <c r="AD15">
         <v>1.25</v>
       </c>
-      <c r="W15">
-        <v>1.01</v>
-      </c>
-      <c r="X15">
-        <v>1.07</v>
-      </c>
-      <c r="Y15">
-        <v>1.55</v>
-      </c>
-      <c r="Z15">
-        <v>2.4</v>
-      </c>
-      <c r="AA15">
-        <v>2.75</v>
-      </c>
-      <c r="AB15">
-        <v>1.4</v>
-      </c>
-      <c r="AC15">
-        <v>5.5</v>
-      </c>
-      <c r="AD15">
-        <v>1.11</v>
-      </c>
       <c r="AE15">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
         <v>2.1</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>1.11</v>
       </c>
       <c r="AK17">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3910,10 +3910,10 @@
         <v>1.9</v>
       </c>
       <c r="S22">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="T22">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="U22">
         <v>3.7</v>
@@ -3949,7 +3949,7 @@
         <v>1.01</v>
       </c>
       <c r="AF22">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AG22">
         <v>1.57</v>
@@ -4067,7 +4067,7 @@
         <v>6.5</v>
       </c>
       <c r="Q23">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R23">
         <v>2.45</v>
@@ -4097,10 +4097,10 @@
         <v>3.95</v>
       </c>
       <c r="AA23">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB23">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC23">
         <v>2.75</v>
@@ -4109,7 +4109,7 @@
         <v>1.42</v>
       </c>
       <c r="AE23">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF23">
         <v>1.9</v>
@@ -4556,16 +4556,16 @@
         <v>1.8</v>
       </c>
       <c r="Q26">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="R26">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="S26">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T26">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="U26">
         <v>2.62</v>
@@ -4574,7 +4574,7 @@
         <v>1.47</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
         <v>1.03</v>
@@ -4586,10 +4586,10 @@
         <v>4.2</v>
       </c>
       <c r="AA26">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB26">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AC26">
         <v>2.88</v>
@@ -4604,7 +4604,7 @@
         <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4722,10 +4722,10 @@
         <v>3.01</v>
       </c>
       <c r="R27">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S27">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="T27">
         <v>2.33</v>
@@ -5051,10 +5051,10 @@
         <v>2.22</v>
       </c>
       <c r="S29">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T29">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="U29">
         <v>2.88</v>
@@ -5066,16 +5066,16 @@
         <v>1.04</v>
       </c>
       <c r="X29">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
         <v>1.3</v>
       </c>
       <c r="Z29">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="AA29">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB29">
         <v>1.83</v>
@@ -5084,16 +5084,16 @@
         <v>3.5</v>
       </c>
       <c r="AD29">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE29">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
         <v>1.8</v>
       </c>
       <c r="AG29">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>4.2</v>
       </c>
       <c r="P30">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="Q30">
         <v>1.89</v>
@@ -5235,19 +5235,19 @@
         <v>1.17</v>
       </c>
       <c r="Z30">
-        <v>4.48</v>
+        <v>4.53</v>
       </c>
       <c r="AA30">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB30">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC30">
         <v>2.49</v>
       </c>
       <c r="AD30">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE30">
         <v>1.14</v>
@@ -5365,7 +5365,7 @@
         <v>1.5</v>
       </c>
       <c r="O31">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P31">
         <v>5.8</v>
@@ -5401,10 +5401,10 @@
         <v>3.6</v>
       </c>
       <c r="AA31">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB31">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AC31">
         <v>3.21</v>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4583,7 +4583,7 @@
         <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA26">
         <v>1.71</v>
@@ -4598,7 +4598,7 @@
         <v>1.4</v>
       </c>
       <c r="AE26">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF26">
         <v>1.67</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="O27">
         <v>3.1</v>
@@ -4876,7 +4876,7 @@
         <v>2.53</v>
       </c>
       <c r="O28">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="P28">
         <v>2.15</v>
@@ -5054,7 +5054,7 @@
         <v>1.4</v>
       </c>
       <c r="T29">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="U29">
         <v>2.88</v>
@@ -5066,7 +5066,7 @@
         <v>1.04</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y29">
         <v>1.3</v>
@@ -5075,7 +5075,7 @@
         <v>3.4</v>
       </c>
       <c r="AA29">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB29">
         <v>1.83</v>
@@ -5087,7 +5087,7 @@
         <v>1.26</v>
       </c>
       <c r="AE29">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF29">
         <v>1.8</v>
@@ -5235,10 +5235,10 @@
         <v>1.17</v>
       </c>
       <c r="Z30">
-        <v>4.53</v>
+        <v>4.46</v>
       </c>
       <c r="AA30">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB30">
         <v>2.15</v>
@@ -5247,7 +5247,7 @@
         <v>2.49</v>
       </c>
       <c r="AD30">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE30">
         <v>1.14</v>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="O6">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="P6">
-        <v>2.79</v>
+        <v>3.11</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="O7">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="P7">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.26</v>
+        <v>2.8</v>
       </c>
       <c r="O9">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2271,7 +2271,7 @@
         <v>3.37</v>
       </c>
       <c r="P12">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O13">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="P13">
         <v>2.15</v>
@@ -2482,10 +2482,10 @@
         <v>1.02</v>
       </c>
       <c r="AF13">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG13">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2926,10 +2926,10 @@
         <v>2.25</v>
       </c>
       <c r="Q16">
-        <v>4.03</v>
+        <v>3.98</v>
       </c>
       <c r="R16">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="S16">
         <v>1.57</v>
@@ -2938,7 +2938,7 @@
         <v>2.2</v>
       </c>
       <c r="U16">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="V16">
         <v>1.21</v>
@@ -2950,13 +2950,13 @@
         <v>1.07</v>
       </c>
       <c r="Y16">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Z16">
         <v>2.38</v>
       </c>
       <c r="AA16">
-        <v>2.61</v>
+        <v>2.51</v>
       </c>
       <c r="AB16">
         <v>1.42</v>
@@ -2974,7 +2974,7 @@
         <v>2.09</v>
       </c>
       <c r="AG16">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3089,10 +3089,10 @@
         <v>4.2</v>
       </c>
       <c r="Q17">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S17">
         <v>1.58</v>
@@ -3113,10 +3113,10 @@
         <v>1.08</v>
       </c>
       <c r="Y17">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z17">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AA17">
         <v>2.5</v>
@@ -3125,7 +3125,7 @@
         <v>1.46</v>
       </c>
       <c r="AC17">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD17">
         <v>1.13</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="P18">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -3421,16 +3421,16 @@
         <v>2.25</v>
       </c>
       <c r="S19">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T19">
         <v>3.2</v>
       </c>
       <c r="U19">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W19">
         <v>1.09</v>
@@ -3442,13 +3442,13 @@
         <v>1.25</v>
       </c>
       <c r="Z19">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA19">
         <v>2.2</v>
       </c>
       <c r="AB19">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC19">
         <v>2.78</v>
@@ -3460,7 +3460,7 @@
         <v>1.13</v>
       </c>
       <c r="AF19">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG19">
         <v>2.15</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK19">
         <v>1.57</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Widad Témara</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.37</v>
+        <v>1.42</v>
       </c>
       <c r="O20">
+        <v>3.9</v>
+      </c>
+      <c r="P20">
+        <v>6.5</v>
+      </c>
+      <c r="Q20">
+        <v>1.85</v>
+      </c>
+      <c r="R20">
+        <v>2.2</v>
+      </c>
+      <c r="S20">
+        <v>1.48</v>
+      </c>
+      <c r="T20">
+        <v>2.78</v>
+      </c>
+      <c r="U20">
         <v>2.8</v>
       </c>
-      <c r="P20">
-        <v>3.2</v>
-      </c>
-      <c r="Q20">
-        <v>3.1</v>
-      </c>
-      <c r="R20">
-        <v>1.78</v>
-      </c>
-      <c r="S20">
-        <v>1.45</v>
-      </c>
-      <c r="T20">
-        <v>2.55</v>
-      </c>
-      <c r="U20">
-        <v>3.4</v>
-      </c>
       <c r="V20">
+        <v>1.36</v>
+      </c>
+      <c r="W20">
+        <v>1.05</v>
+      </c>
+      <c r="X20">
+        <v>1.04</v>
+      </c>
+      <c r="Y20">
+        <v>1.31</v>
+      </c>
+      <c r="Z20">
+        <v>2.92</v>
+      </c>
+      <c r="AA20">
+        <v>1.99</v>
+      </c>
+      <c r="AB20">
+        <v>1.7</v>
+      </c>
+      <c r="AC20">
+        <v>3.28</v>
+      </c>
+      <c r="AD20">
         <v>1.25</v>
       </c>
-      <c r="W20">
-        <v>1.04</v>
-      </c>
-      <c r="X20">
+      <c r="AE20">
         <v>1.06</v>
       </c>
-      <c r="Y20">
-        <v>1.45</v>
-      </c>
-      <c r="Z20">
-        <v>2.41</v>
-      </c>
-      <c r="AA20">
-        <v>2.46</v>
-      </c>
-      <c r="AB20">
-        <v>1.46</v>
-      </c>
-      <c r="AC20">
-        <v>4.8</v>
-      </c>
-      <c r="AD20">
-        <v>1.14</v>
-      </c>
-      <c r="AE20">
-        <v>1.02</v>
-      </c>
       <c r="AF20">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG20">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="AK20">
-        <v>1.53</v>
+        <v>2.62</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Widad Témara</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="O21">
-        <v>3.65</v>
+        <v>2.87</v>
       </c>
       <c r="P21">
-        <v>8.4</v>
+        <v>3</v>
       </c>
       <c r="Q21">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="R21">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="S21">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="T21">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="U21">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="V21">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y21">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="Z21">
-        <v>2.92</v>
+        <v>2.41</v>
       </c>
       <c r="AA21">
-        <v>1.99</v>
+        <v>2.46</v>
       </c>
       <c r="AB21">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AC21">
-        <v>3.28</v>
+        <v>4.8</v>
       </c>
       <c r="AD21">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AE21">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF21">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="AG21">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="AK21">
-        <v>2.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4221,25 +4221,25 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="O24">
         <v>2.65</v>
       </c>
       <c r="P24">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q24">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R24">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S24">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="T24">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="U24">
         <v>4</v>
@@ -4248,37 +4248,37 @@
         <v>1.2</v>
       </c>
       <c r="W24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
         <v>1.09</v>
       </c>
       <c r="Y24">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Z24">
         <v>2.4</v>
       </c>
       <c r="AA24">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="AB24">
         <v>1.44</v>
       </c>
       <c r="AC24">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AD24">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE24">
         <v>1.01</v>
       </c>
       <c r="AF24">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AG24">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.4</v>
       </c>
       <c r="AK24">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.61</v>
+        <v>2.81</v>
       </c>
       <c r="O25">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="P25">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="Q25">
         <v>0</v>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -635,43 +635,43 @@
         </is>
       </c>
       <c r="N2">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="O2">
         <v>3.2</v>
       </c>
       <c r="P2">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="Q2">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T2">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="U2">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
+        <v>1.04</v>
+      </c>
+      <c r="X2">
         <v>1.05</v>
       </c>
-      <c r="X2">
-        <v>1.06</v>
-      </c>
       <c r="Y2">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z2">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA2">
         <v>2.2</v>
@@ -680,19 +680,19 @@
         <v>1.65</v>
       </c>
       <c r="AC2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD2">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE2">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF2">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG2">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -819,7 +819,7 @@
         <v>2.95</v>
       </c>
       <c r="U3">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V3">
         <v>1.41</v>
@@ -828,7 +828,7 @@
         <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
         <v>1.25</v>
@@ -843,10 +843,10 @@
         <v>1.8</v>
       </c>
       <c r="AC3">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD3">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE3">
         <v>1.09</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
         <v>2.2</v>
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O10">
         <v>3.2</v>
       </c>
       <c r="P10">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="Q10">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="R10">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="S10">
         <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="U10">
         <v>2.76</v>
@@ -1969,7 +1969,7 @@
         <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
         <v>1.28</v>
@@ -1978,25 +1978,25 @@
         <v>3.08</v>
       </c>
       <c r="AA10">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB10">
         <v>1.75</v>
       </c>
       <c r="AC10">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD10">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE10">
         <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="O14">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P14">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q14">
         <v>3.5</v>
@@ -2609,16 +2609,16 @@
         <v>1.5</v>
       </c>
       <c r="T14">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U14">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="V14">
         <v>1.25</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
         <v>1.07</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="O15">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P15">
-        <v>5.39</v>
+        <v>5.75</v>
       </c>
       <c r="Q15">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R15">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="S15">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T15">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="U15">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="V15">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="Z15">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="AA15">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB15">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC15">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD15">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE15">
         <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG15">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -4070,7 +4070,7 @@
         <v>1.85</v>
       </c>
       <c r="R23">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="S23">
         <v>1.28</v>
@@ -4085,7 +4085,7 @@
         <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
         <v>1.02</v>
@@ -4097,16 +4097,16 @@
         <v>3.95</v>
       </c>
       <c r="AA23">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB23">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AC23">
         <v>2.75</v>
       </c>
       <c r="AD23">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE23">
         <v>1.16</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="O25">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="P25">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4568,7 +4568,7 @@
         <v>2.89</v>
       </c>
       <c r="U26">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="V26">
         <v>1.47</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="O27">
         <v>3.1</v>
@@ -4719,16 +4719,16 @@
         <v>2.8</v>
       </c>
       <c r="Q27">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="R27">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S27">
         <v>1.51</v>
       </c>
       <c r="T27">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="U27">
         <v>3.32</v>
@@ -4749,13 +4749,13 @@
         <v>2.7</v>
       </c>
       <c r="AA27">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AB27">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AC27">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AD27">
         <v>1.15</v>
@@ -4764,10 +4764,10 @@
         <v>1.03</v>
       </c>
       <c r="AF27">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AG27">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.53</v>
+        <v>3.1</v>
       </c>
       <c r="O28">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q28">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S28">
         <v>1.35</v>
@@ -4915,7 +4915,7 @@
         <v>1.9</v>
       </c>
       <c r="AB28">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC28">
         <v>3.25</v>
@@ -4927,10 +4927,10 @@
         <v>1.07</v>
       </c>
       <c r="AF28">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG28">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AK28">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="O29">
         <v>3.12</v>
@@ -5045,10 +5045,10 @@
         <v>3.2</v>
       </c>
       <c r="Q29">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="R29">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="S29">
         <v>1.4</v>
@@ -5069,10 +5069,10 @@
         <v>1.05</v>
       </c>
       <c r="Y29">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z29">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA29">
         <v>2</v>
@@ -5087,7 +5087,7 @@
         <v>1.26</v>
       </c>
       <c r="AE29">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF29">
         <v>1.8</v>
@@ -5205,13 +5205,13 @@
         <v>4.2</v>
       </c>
       <c r="P30">
-        <v>5.55</v>
+        <v>5.25</v>
       </c>
       <c r="Q30">
         <v>1.89</v>
       </c>
       <c r="R30">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="S30">
         <v>1.29</v>
@@ -5220,7 +5220,7 @@
         <v>3.4</v>
       </c>
       <c r="U30">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="V30">
         <v>1.5</v>
@@ -5235,10 +5235,10 @@
         <v>1.17</v>
       </c>
       <c r="Z30">
-        <v>4.46</v>
+        <v>4.45</v>
       </c>
       <c r="AA30">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AB30">
         <v>2.15</v>
@@ -5401,19 +5401,19 @@
         <v>3.6</v>
       </c>
       <c r="AA31">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AB31">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC31">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="AD31">
         <v>1.3</v>
       </c>
       <c r="AE31">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF31">
         <v>1.95</v>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O16">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P16">
         <v>2.25</v>
       </c>
       <c r="Q16">
-        <v>3.98</v>
+        <v>4.04</v>
       </c>
       <c r="R16">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="S16">
         <v>1.57</v>
@@ -2938,7 +2938,7 @@
         <v>2.2</v>
       </c>
       <c r="U16">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="V16">
         <v>1.21</v>
@@ -2950,13 +2950,13 @@
         <v>1.07</v>
       </c>
       <c r="Y16">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Z16">
         <v>2.38</v>
       </c>
       <c r="AA16">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="AB16">
         <v>1.42</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O17">
         <v>3</v>
       </c>
       <c r="P17">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q17">
         <v>2.54</v>
@@ -3910,10 +3910,10 @@
         <v>1.9</v>
       </c>
       <c r="S22">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="T22">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="U22">
         <v>3.7</v>
@@ -3946,10 +3946,10 @@
         <v>1.14</v>
       </c>
       <c r="AE22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF22">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AG22">
         <v>1.57</v>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -631,17 +631,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O2">
         <v>3.2</v>
       </c>
       <c r="P2">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q2">
         <v>5.25</v>
@@ -650,10 +650,10 @@
         <v>2.05</v>
       </c>
       <c r="S2">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.47</v>
+        <v>2.58</v>
       </c>
       <c r="U2">
         <v>2.91</v>
@@ -680,10 +680,10 @@
         <v>1.65</v>
       </c>
       <c r="AC2">
-        <v>4.1</v>
+        <v>3.92</v>
       </c>
       <c r="AD2">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE2">
         <v>1.04</v>
@@ -775,26 +775,26 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -807,34 +807,34 @@
         <v>4.88</v>
       </c>
       <c r="Q3">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="R3">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S3">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="U3">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V3">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
         <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z3">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA3">
         <v>2</v>
@@ -843,10 +843,10 @@
         <v>1.8</v>
       </c>
       <c r="AC3">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE3">
         <v>1.09</v>
@@ -855,50 +855,50 @@
         <v>1.85</v>
       </c>
       <c r="AG3">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "49"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "64"]</t>
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AK3">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -2603,19 +2603,19 @@
         <v>3.5</v>
       </c>
       <c r="R14">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="S14">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="T14">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="U14">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="V14">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="W14">
         <v>1.04</v>
@@ -2627,7 +2627,7 @@
         <v>1.55</v>
       </c>
       <c r="Z14">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="AA14">
         <v>2.75</v>
@@ -2636,19 +2636,19 @@
         <v>1.4</v>
       </c>
       <c r="AC14">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AD14">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF14">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG14">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AK14">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2757,22 +2757,22 @@
         <v>1.49</v>
       </c>
       <c r="O15">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
         <v>5.75</v>
       </c>
       <c r="Q15">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="R15">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="S15">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T15">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U15">
         <v>2.97</v>
@@ -2796,7 +2796,7 @@
         <v>2.1</v>
       </c>
       <c r="AB15">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC15">
         <v>3.8</v>
@@ -2811,7 +2811,7 @@
         <v>2.2</v>
       </c>
       <c r="AG15">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK15">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -938,130 +938,130 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R4">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S4">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T4">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="U4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="Z4">
-        <v>2.88</v>
+        <v>2.54</v>
       </c>
       <c r="AA4">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AB4">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AC4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD4">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE4">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AG4">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "60", "65"]</t>
         </is>
       </c>
       <c r="AJ4">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,103 +1101,103 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="O5">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="P5">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9"]</t>
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1264,103 +1264,103 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="O6">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="P6">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18"]</t>
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1427,103 +1427,103 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="O7">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P7">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
+          <t>["24", "69", "90+11"]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1590,103 +1590,103 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
+        <v>2.45</v>
+      </c>
+      <c r="O8">
+        <v>2.9</v>
+      </c>
+      <c r="P8">
+        <v>2.85</v>
+      </c>
+      <c r="Q8">
+        <v>3.18</v>
+      </c>
+      <c r="R8">
+        <v>1.89</v>
+      </c>
+      <c r="S8">
+        <v>1.5</v>
+      </c>
+      <c r="T8">
+        <v>2.29</v>
+      </c>
+      <c r="U8">
+        <v>3.38</v>
+      </c>
+      <c r="V8">
+        <v>1.24</v>
+      </c>
+      <c r="W8">
+        <v>1.01</v>
+      </c>
+      <c r="X8">
+        <v>1.05</v>
+      </c>
+      <c r="Y8">
+        <v>1.44</v>
+      </c>
+      <c r="Z8">
+        <v>2.43</v>
+      </c>
+      <c r="AA8">
         <v>2.41</v>
       </c>
-      <c r="O8">
-        <v>2.93</v>
-      </c>
-      <c r="P8">
-        <v>2.86</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0</v>
-      </c>
-      <c r="X8">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>0</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["74"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28"]</t>
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1756,27 +1756,27 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="O9">
         <v>3.4</v>
@@ -1785,10 +1785,10 @@
         <v>2.1</v>
       </c>
       <c r="Q9">
-        <v>3.28</v>
+        <v>3.66</v>
       </c>
       <c r="R9">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
         <v>1.25</v>
@@ -1797,10 +1797,10 @@
         <v>3.3</v>
       </c>
       <c r="U9">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="V9">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W9">
         <v>1.1</v>
@@ -1809,16 +1809,16 @@
         <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z9">
-        <v>4.41</v>
+        <v>4.2</v>
       </c>
       <c r="AA9">
         <v>1.63</v>
       </c>
       <c r="AB9">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC9">
         <v>2.56</v>
@@ -1830,7 +1830,7 @@
         <v>1.12</v>
       </c>
       <c r="AF9">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG9">
         <v>2.38</v>
@@ -1842,41 +1842,41 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "67", "72", "90"]</t>
         </is>
       </c>
       <c r="AJ9">
         <v>1.21</v>
       </c>
       <c r="AK9">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1919,127 +1919,127 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="O10">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="Q10">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="R10">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S10">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="U10">
-        <v>2.76</v>
+        <v>2.57</v>
       </c>
       <c r="V10">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z10">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AA10">
         <v>2.05</v>
       </c>
       <c r="AB10">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AC10">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AD10">
+        <v>1.32</v>
+      </c>
+      <c r="AE10">
+        <v>1.09</v>
+      </c>
+      <c r="AF10">
+        <v>1.64</v>
+      </c>
+      <c r="AG10">
+        <v>2.04</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>["39", "83", "88"]</t>
+        </is>
+      </c>
+      <c r="AJ10">
         <v>1.26</v>
       </c>
-      <c r="AE10">
-        <v>1.06</v>
-      </c>
-      <c r="AF10">
-        <v>1.75</v>
-      </c>
-      <c r="AG10">
-        <v>1.9</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.22</v>
-      </c>
       <c r="AK10">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="O11">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P11">
-        <v>5.36</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O12">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O13">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P13">
         <v>2.15</v>
       </c>
       <c r="Q13">
-        <v>4.32</v>
+        <v>4.55</v>
       </c>
       <c r="R13">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="S13">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T13">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="U13">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="V13">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="W13">
         <v>1.03</v>
       </c>
       <c r="X13">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y13">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="Z13">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AA13">
-        <v>2.21</v>
+        <v>2.66</v>
       </c>
       <c r="AB13">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AC13">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="AD13">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG13">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.36</v>
       </c>
       <c r="AK13">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,90 +2559,90 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="O14">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="P14">
-        <v>2.6</v>
+        <v>5.75</v>
       </c>
       <c r="Q14">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="R14">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="S14">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="T14">
-        <v>2.11</v>
+        <v>2.65</v>
       </c>
       <c r="U14">
+        <v>2.97</v>
+      </c>
+      <c r="V14">
+        <v>1.36</v>
+      </c>
+      <c r="W14">
+        <v>1.07</v>
+      </c>
+      <c r="X14">
+        <v>1.02</v>
+      </c>
+      <c r="Y14">
+        <v>1.35</v>
+      </c>
+      <c r="Z14">
+        <v>3.08</v>
+      </c>
+      <c r="AA14">
+        <v>2.1</v>
+      </c>
+      <c r="AB14">
+        <v>1.7</v>
+      </c>
+      <c r="AC14">
         <v>3.8</v>
       </c>
-      <c r="V14">
-        <v>1.19</v>
-      </c>
-      <c r="W14">
-        <v>1.04</v>
-      </c>
-      <c r="X14">
-        <v>1.07</v>
-      </c>
-      <c r="Y14">
-        <v>1.55</v>
-      </c>
-      <c r="Z14">
-        <v>2.24</v>
-      </c>
-      <c r="AA14">
-        <v>2.75</v>
-      </c>
-      <c r="AB14">
-        <v>1.4</v>
-      </c>
-      <c r="AC14">
-        <v>5.3</v>
-      </c>
       <c r="AD14">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AE14">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
         <v>2.2</v>
@@ -2652,46 +2652,46 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "39", "76"]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "45+1", "70"]</t>
         </is>
       </c>
       <c r="AJ14">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AK14">
-        <v>1.32</v>
+        <v>2.45</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G15">
@@ -2750,65 +2750,65 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N15">
-        <v>1.49</v>
+        <v>2.75</v>
       </c>
       <c r="O15">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="P15">
-        <v>5.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q15">
-        <v>2.05</v>
+        <v>3.5</v>
       </c>
       <c r="R15">
+        <v>1.83</v>
+      </c>
+      <c r="S15">
+        <v>1.62</v>
+      </c>
+      <c r="T15">
+        <v>2.11</v>
+      </c>
+      <c r="U15">
+        <v>3.8</v>
+      </c>
+      <c r="V15">
+        <v>1.19</v>
+      </c>
+      <c r="W15">
+        <v>1.04</v>
+      </c>
+      <c r="X15">
+        <v>1.07</v>
+      </c>
+      <c r="Y15">
+        <v>1.55</v>
+      </c>
+      <c r="Z15">
+        <v>2.24</v>
+      </c>
+      <c r="AA15">
+        <v>2.75</v>
+      </c>
+      <c r="AB15">
+        <v>1.4</v>
+      </c>
+      <c r="AC15">
+        <v>5.3</v>
+      </c>
+      <c r="AD15">
+        <v>1.11</v>
+      </c>
+      <c r="AE15">
+        <v>1.03</v>
+      </c>
+      <c r="AF15">
         <v>2.15</v>
-      </c>
-      <c r="S15">
-        <v>1.38</v>
-      </c>
-      <c r="T15">
-        <v>2.65</v>
-      </c>
-      <c r="U15">
-        <v>2.97</v>
-      </c>
-      <c r="V15">
-        <v>1.35</v>
-      </c>
-      <c r="W15">
-        <v>1.07</v>
-      </c>
-      <c r="X15">
-        <v>1.02</v>
-      </c>
-      <c r="Y15">
-        <v>1.35</v>
-      </c>
-      <c r="Z15">
-        <v>2.98</v>
-      </c>
-      <c r="AA15">
-        <v>2.1</v>
-      </c>
-      <c r="AB15">
-        <v>1.72</v>
-      </c>
-      <c r="AC15">
-        <v>3.8</v>
-      </c>
-      <c r="AD15">
-        <v>1.22</v>
-      </c>
-      <c r="AE15">
-        <v>1.06</v>
-      </c>
-      <c r="AF15">
-        <v>2.2</v>
       </c>
       <c r="AG15">
         <v>1.6</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AK15">
-        <v>2.45</v>
+        <v>1.32</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2920,61 +2920,61 @@
         <v>3.1</v>
       </c>
       <c r="O16">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="P16">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q16">
-        <v>4.04</v>
+        <v>4.13</v>
       </c>
       <c r="R16">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="S16">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="T16">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="U16">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="V16">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="W16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y16">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="Z16">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AA16">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AB16">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AC16">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AD16">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AE16">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF16">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AG16">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3083,61 +3083,61 @@
         <v>1.85</v>
       </c>
       <c r="O17">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P17">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="Q17">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="R17">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="S17">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="T17">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U17">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="V17">
         <v>1.22</v>
       </c>
       <c r="W17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X17">
+        <v>1.1</v>
+      </c>
+      <c r="Y17">
+        <v>1.66</v>
+      </c>
+      <c r="Z17">
+        <v>2.18</v>
+      </c>
+      <c r="AA17">
+        <v>3</v>
+      </c>
+      <c r="AB17">
+        <v>1.36</v>
+      </c>
+      <c r="AC17">
+        <v>5.5</v>
+      </c>
+      <c r="AD17">
         <v>1.08</v>
       </c>
-      <c r="Y17">
-        <v>1.52</v>
-      </c>
-      <c r="Z17">
-        <v>2.43</v>
-      </c>
-      <c r="AA17">
-        <v>2.5</v>
-      </c>
-      <c r="AB17">
-        <v>1.46</v>
-      </c>
-      <c r="AC17">
-        <v>3.5</v>
-      </c>
-      <c r="AD17">
-        <v>1.13</v>
-      </c>
       <c r="AE17">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF17">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="AG17">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.11</v>
       </c>
       <c r="AK17">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="O18">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="P18">
-        <v>2.74</v>
+        <v>3.18</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Widad Témara</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="O20">
-        <v>3.9</v>
+        <v>2.87</v>
       </c>
       <c r="P20">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="Q20">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="R20">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="S20">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="T20">
-        <v>2.78</v>
+        <v>2.25</v>
       </c>
       <c r="U20">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="V20">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y20">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="Z20">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="AA20">
-        <v>1.99</v>
+        <v>2.46</v>
       </c>
       <c r="AB20">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC20">
-        <v>3.28</v>
+        <v>4.8</v>
       </c>
       <c r="AD20">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AE20">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AF20">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG20">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AK20">
-        <v>2.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Widad Témara</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="O21">
-        <v>2.87</v>
+        <v>3.9</v>
       </c>
       <c r="P21">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="Q21">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="R21">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="S21">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="T21">
-        <v>2.55</v>
+        <v>2.77</v>
       </c>
       <c r="U21">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="V21">
+        <v>1.31</v>
+      </c>
+      <c r="W21">
+        <v>1.05</v>
+      </c>
+      <c r="X21">
+        <v>1.03</v>
+      </c>
+      <c r="Y21">
+        <v>1.31</v>
+      </c>
+      <c r="Z21">
+        <v>2.92</v>
+      </c>
+      <c r="AA21">
+        <v>2</v>
+      </c>
+      <c r="AB21">
+        <v>1.73</v>
+      </c>
+      <c r="AC21">
+        <v>3.8</v>
+      </c>
+      <c r="AD21">
         <v>1.25</v>
       </c>
-      <c r="W21">
-        <v>1.04</v>
-      </c>
-      <c r="X21">
+      <c r="AE21">
         <v>1.06</v>
       </c>
-      <c r="Y21">
-        <v>1.45</v>
-      </c>
-      <c r="Z21">
-        <v>2.41</v>
-      </c>
-      <c r="AA21">
-        <v>2.46</v>
-      </c>
-      <c r="AB21">
-        <v>1.46</v>
-      </c>
-      <c r="AC21">
-        <v>4.8</v>
-      </c>
-      <c r="AD21">
-        <v>1.14</v>
-      </c>
-      <c r="AE21">
-        <v>1.02</v>
-      </c>
       <c r="AF21">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AG21">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="AK21">
-        <v>1.53</v>
+        <v>2.62</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O22">
         <v>2.9</v>
       </c>
       <c r="P22">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q22">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="R22">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S22">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="T22">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="U22">
         <v>3.7</v>
@@ -3934,22 +3934,22 @@
         <v>2.33</v>
       </c>
       <c r="AA22">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AB22">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AC22">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AD22">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE22">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF22">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AG22">
         <v>1.57</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AK22">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,22 +4221,22 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="O24">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="P24">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q24">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="R24">
         <v>1.91</v>
       </c>
       <c r="S24">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="T24">
         <v>2.1</v>
@@ -4254,19 +4254,19 @@
         <v>1.09</v>
       </c>
       <c r="Y24">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Z24">
         <v>2.4</v>
       </c>
       <c r="AA24">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AB24">
         <v>1.44</v>
       </c>
       <c r="AC24">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AD24">
         <v>1.11</v>
@@ -4275,10 +4275,10 @@
         <v>1.01</v>
       </c>
       <c r="AF24">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AG24">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK24">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O25">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="P25">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="Q25">
         <v>0</v>

--- a/jogos_2026-10-08.xlsx
+++ b/jogos_2026-10-08.xlsx
@@ -2079,26 +2079,26 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "40", "47", "54", "67", "81"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1"]</t>
         </is>
       </c>
       <c r="AJ11">
@@ -2242,26 +2242,26 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38", "60"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["78"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -2906,14 +2906,14 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3165,10 +3165,10 @@
         <v>-1</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ17">
         <v>0</v>
@@ -3177,10 +3177,10 @@
         <v>0</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,26 +3220,26 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38", "78", "90+3"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+10", "48"]</t>
         </is>
       </c>
       <c r="AJ18">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3383,13 +3383,13 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3398,11 +3398,11 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3415,25 +3415,25 @@
         <v>2.48</v>
       </c>
       <c r="Q19">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="R19">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S19">
         <v>1.33</v>
       </c>
       <c r="T19">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U19">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V19">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="W19">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
         <v>1.05</v>
@@ -3442,71 +3442,71 @@
         <v>1.25</v>
       </c>
       <c r="Z19">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AA19">
         <v>2.2</v>
       </c>
       <c r="AB19">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AC19">
-        <v>2.78</v>
+        <v>2.46</v>
       </c>
       <c r="AD19">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AE19">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF19">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG19">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51", "55", "71"]</t>
         </is>
       </c>
       <c r="AJ19">
+        <v>1.33</v>
+      </c>
+      <c r="AK19">
         <v>1.4</v>
       </c>
-      <c r="AK19">
-        <v>1.57</v>
-      </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3537,16 +3537,16 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Widad Témara</t>
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -3558,118 +3558,118 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="O20">
-        <v>2.87</v>
+        <v>3.9</v>
       </c>
       <c r="P20">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="Q20">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="R20">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="T20">
-        <v>2.25</v>
+        <v>2.77</v>
       </c>
       <c r="U20">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="V20">
+        <v>1.31</v>
+      </c>
+      <c r="W20">
+        <v>1.05</v>
+      </c>
+      <c r="X20">
+        <v>1.03</v>
+      </c>
+      <c r="Y20">
+        <v>1.31</v>
+      </c>
+      <c r="Z20">
+        <v>2.92</v>
+      </c>
+      <c r="AA20">
+        <v>2</v>
+      </c>
+      <c r="AB20">
+        <v>1.73</v>
+      </c>
+      <c r="AC20">
+        <v>3.8</v>
+      </c>
+      <c r="AD20">
         <v>1.25</v>
       </c>
-      <c r="W20">
-        <v>1.04</v>
-      </c>
-      <c r="X20">
+      <c r="AE20">
         <v>1.06</v>
       </c>
-      <c r="Y20">
-        <v>1.45</v>
-      </c>
-      <c r="Z20">
-        <v>2.6</v>
-      </c>
-      <c r="AA20">
-        <v>2.46</v>
-      </c>
-      <c r="AB20">
-        <v>1.5</v>
-      </c>
-      <c r="AC20">
-        <v>4.8</v>
-      </c>
-      <c r="AD20">
-        <v>1.14</v>
-      </c>
-      <c r="AE20">
-        <v>1</v>
-      </c>
       <c r="AF20">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG20">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
+          <t>["63"]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ20">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="AK20">
-        <v>1.53</v>
+        <v>2.62</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Widad Témara</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="O21">
-        <v>3.9</v>
+        <v>2.87</v>
       </c>
       <c r="P21">
-        <v>6.75</v>
+        <v>3</v>
       </c>
       <c r="Q21">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="R21">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="S21">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="T21">
-        <v>2.77</v>
+        <v>2.25</v>
       </c>
       <c r="U21">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="V21">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y21">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="Z21">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="AA21">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="AB21">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AC21">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AD21">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AE21">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AF21">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG21">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AK21">
-        <v>2.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="O23">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P23">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="R23">
-        <v>2.59</v>
+        <v>2.71</v>
       </c>
       <c r="S23">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T23">
-        <v>3.22</v>
+        <v>3.32</v>
       </c>
       <c r="U23">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="V23">
         <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
+        <v>1.16</v>
+      </c>
+      <c r="Z23">
+        <v>4.15</v>
+      </c>
+      <c r="AA23">
+        <v>1.69</v>
+      </c>
+      <c r="AB23">
+        <v>2.24</v>
+      </c>
+      <c r="AC23">
+        <v>2.56</v>
+      </c>
+      <c r="AD23">
+        <v>1.47</v>
+      </c>
+      <c r="AE23">
         <v>1.17</v>
       </c>
-      <c r="Z23">
-        <v>3.95</v>
-      </c>
-      <c r="AA23">
-        <v>1.74</v>
-      </c>
-      <c r="AB23">
-        <v>2.15</v>
-      </c>
-      <c r="AC23">
-        <v>2.75</v>
-      </c>
-      <c r="AD23">
-        <v>1.43</v>
-      </c>
-      <c r="AE23">
-        <v>1.16</v>
-      </c>
       <c r="AF23">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG23">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK23">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4242,10 +4242,10 @@
         <v>2.1</v>
       </c>
       <c r="U24">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="V24">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W24">
         <v>1.04</v>
@@ -4257,10 +4257,10 @@
         <v>1.51</v>
       </c>
       <c r="Z24">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AA24">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AB24">
         <v>1.44</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>4.12</v>
+        <v>4.24</v>
       </c>
       <c r="O26">
         <v>3.8</v>
@@ -4562,49 +4562,49 @@
         <v>2.3</v>
       </c>
       <c r="S26">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T26">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="U26">
+        <v>2.31</v>
+      </c>
+      <c r="V26">
+        <v>1.52</v>
+      </c>
+      <c r="W26">
+        <v>1.12</v>
+      </c>
+      <c r="X26">
+        <v>1.01</v>
+      </c>
+      <c r="Y26">
+        <v>1.2</v>
+      </c>
+      <c r="Z26">
+        <v>4.5</v>
+      </c>
+      <c r="AA26">
+        <v>1.6</v>
+      </c>
+      <c r="AB26">
+        <v>2.15</v>
+      </c>
+      <c r="AC26">
         <v>2.63</v>
       </c>
-      <c r="V26">
+      <c r="AD26">
         <v>1.47</v>
       </c>
-      <c r="W26">
-        <v>1.1</v>
-      </c>
-      <c r="X26">
-        <v>1.03</v>
-      </c>
-      <c r="Y26">
-        <v>1.22</v>
-      </c>
-      <c r="Z26">
-        <v>4.1</v>
-      </c>
-      <c r="AA26">
-        <v>1.71</v>
-      </c>
-      <c r="AB26">
-        <v>1.98</v>
-      </c>
-      <c r="AC26">
-        <v>2.88</v>
-      </c>
-      <c r="AD26">
-        <v>1.4</v>
-      </c>
       <c r="AE26">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF26">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG26">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK26">
         <v>1.22</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.36</v>
+        <v>3.8</v>
       </c>
       <c r="O27">
+        <v>3.4</v>
+      </c>
+      <c r="P27">
+        <v>1.8</v>
+      </c>
+      <c r="Q27">
+        <v>4.76</v>
+      </c>
+      <c r="R27">
+        <v>2.2</v>
+      </c>
+      <c r="S27">
+        <v>1.3</v>
+      </c>
+      <c r="T27">
         <v>3.1</v>
       </c>
-      <c r="P27">
-        <v>2.8</v>
-      </c>
-      <c r="Q27">
-        <v>3.1</v>
-      </c>
-      <c r="R27">
-        <v>1.95</v>
-      </c>
-      <c r="S27">
-        <v>1.51</v>
-      </c>
-      <c r="T27">
-        <v>2.34</v>
-      </c>
       <c r="U27">
-        <v>3.32</v>
+        <v>2.5</v>
       </c>
       <c r="V27">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="Z27">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA27">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AB27">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AC27">
-        <v>4.25</v>
+        <v>2.88</v>
       </c>
       <c r="AD27">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AE27">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF27">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AG27">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AK27">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,80 +4873,80 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="O28">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P28">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="Q28">
-        <v>4</v>
+        <v>3.17</v>
       </c>
       <c r="R28">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="T28">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="U28">
-        <v>2.7</v>
+        <v>3.24</v>
       </c>
       <c r="V28">
+        <v>1.28</v>
+      </c>
+      <c r="W28">
+        <v>1.02</v>
+      </c>
+      <c r="X28">
+        <v>1.07</v>
+      </c>
+      <c r="Y28">
         <v>1.4</v>
       </c>
-      <c r="W28">
-        <v>1.07</v>
-      </c>
-      <c r="X28">
-        <v>1.04</v>
-      </c>
-      <c r="Y28">
-        <v>1.29</v>
-      </c>
       <c r="Z28">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="AA28">
-        <v>1.9</v>
+        <v>2.27</v>
       </c>
       <c r="AB28">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="AC28">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="AD28">
+        <v>1.16</v>
+      </c>
+      <c r="AE28">
+        <v>1.03</v>
+      </c>
+      <c r="AF28">
+        <v>1.93</v>
+      </c>
+      <c r="AG28">
+        <v>1.76</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
         <v>1.33</v>
       </c>
-      <c r="AE28">
-        <v>1.07</v>
-      </c>
-      <c r="AF28">
-        <v>1.73</v>
-      </c>
-      <c r="AG28">
-        <v>2.1</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.65</v>
-      </c>
       <c r="AK28">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5039,25 +5039,25 @@
         <v>2.13</v>
       </c>
       <c r="O29">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="P29">
         <v>3.2</v>
       </c>
       <c r="Q29">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="R29">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="S29">
         <v>1.4</v>
       </c>
       <c r="T29">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="U29">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="V29">
         <v>1.4</v>
@@ -5069,10 +5069,10 @@
         <v>1.05</v>
       </c>
       <c r="Y29">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z29">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AA29">
         <v>2</v>
@@ -5087,7 +5087,7 @@
         <v>1.26</v>
       </c>
       <c r="AE29">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF29">
         <v>1.8</v>
@@ -5109,7 +5109,7 @@
         <v>1.24</v>
       </c>
       <c r="AK29">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O30">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P30">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="Q30">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="R30">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="S30">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U30">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="V30">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="W30">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z30">
-        <v>4.45</v>
+        <v>5.16</v>
       </c>
       <c r="AA30">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AB30">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AC30">
-        <v>2.49</v>
+        <v>2.26</v>
       </c>
       <c r="AD30">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AE30">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF30">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="O31">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P31">
         <v>5.8</v>
@@ -5374,52 +5374,52 @@
         <v>2</v>
       </c>
       <c r="R31">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="S31">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="T31">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="U31">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="V31">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="W31">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z31">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA31">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AB31">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AC31">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AD31">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE31">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF31">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AG31">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AL31">
         <v>0</v>
